--- a/Excel/CalcGrower_v0.1.xlsx
+++ b/Excel/CalcGrower_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jefferson\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A25E67F-7827-467A-86EF-AF14B37F6D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63897DF2-A9E3-422E-B6B0-4575DEA32A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="96">
   <si>
     <t>Fabricante</t>
   </si>
@@ -266,9 +264,6 @@
     <t>Molibdênio (Mo)</t>
   </si>
   <si>
-    <t>Totais</t>
-  </si>
-  <si>
     <t>N%</t>
   </si>
   <si>
@@ -305,13 +300,34 @@
     <t>Mo%</t>
   </si>
   <si>
-    <t>Coluna1</t>
-  </si>
-  <si>
     <t>Formula</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Nutriente</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Macronutrientes</t>
+  </si>
+  <si>
+    <t>Micronutrientes</t>
+  </si>
+  <si>
+    <t>Elemnto Principal</t>
+  </si>
+  <si>
+    <t>Micro</t>
+  </si>
+  <si>
+    <t>ppm</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -492,7 +508,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -522,7 +538,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -552,284 +568,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="57">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
+  <dxfs count="59">
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1170,6 +924,50 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1225,6 +1023,16 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1232,7 +1040,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1246,6 +1054,7 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1253,22 +1062,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1276,22 +1086,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1299,22 +1110,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1322,22 +1134,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1345,22 +1158,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1368,22 +1182,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1391,22 +1206,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1414,22 +1230,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1437,22 +1254,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1460,22 +1278,23 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1483,7 +1302,295 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1555,16 +1662,37 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1577,62 +1705,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -1698,8 +1770,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:T7" totalsRowShown="0" headerRowDxfId="55">
-  <autoFilter ref="A1:T7" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="21">
+  <autoFilter ref="A1:V7" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1720,35 +1792,39 @@
     <filterColumn colId="17" hiddenButton="1"/>
     <filterColumn colId="18" hiddenButton="1"/>
     <filterColumn colId="19" hiddenButton="1"/>
+    <filterColumn colId="20" hiddenButton="1"/>
+    <filterColumn colId="21" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="12"/>
+  <tableColumns count="22">
+    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="0"/>
+    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AA7" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="53" tableBorderDxfId="54" totalsRowBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AA7" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
   <autoFilter ref="A1:AA7" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1779,71 +1855,95 @@
     <filterColumn colId="26" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{071368D0-EBC2-4032-93AC-5DB90A2BD224}" name="ID" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N%" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{071368D0-EBC2-4032-93AC-5DB90A2BD224}" name="ID" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N%" dataDxfId="50">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P%" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P%" dataDxfId="49">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K%" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K%" dataDxfId="48">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[K],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca%" dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca%" dataDxfId="47">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg%" dataDxfId="7">
+    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg%" dataDxfId="46">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S%" dataDxfId="6">
+    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S%" dataDxfId="45">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[S],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe%" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe%" dataDxfId="44">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn%" dataDxfId="4">
+    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn%" dataDxfId="43">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn%" dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn%" dataDxfId="42">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B%" dataDxfId="2">
+    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B%" dataDxfId="41">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[B],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu%" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu%" dataDxfId="40">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo%" dataDxfId="0">
+    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo%" dataDxfId="39">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="42"/>
-    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="41"/>
-    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="39"/>
-    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="38"/>
-    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="37"/>
-    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="36"/>
-    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="35"/>
-    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="34"/>
-    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="38">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="37">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="36">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="35">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="34">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="33">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="32">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="31">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="30">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="29">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="28">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="27">
+      <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="Tabela3" displayName="Tabela3" ref="A10:B22" totalsRowShown="0" headerRowDxfId="48" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="Tabela3" displayName="Tabela3" ref="A10:B22" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A10:B22" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Totais" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Coluna1" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2155,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620928F-272B-43F4-861A-5D8E0480B12C}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -2177,9 +2277,11 @@
     <col min="18" max="18" width="15.140625" customWidth="1"/>
     <col min="19" max="19" width="22.85546875" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" customWidth="1"/>
+    <col min="21" max="21" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -2190,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>41</v>
@@ -2240,8 +2342,14 @@
       <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -2253,45 +2361,33 @@
       <c r="E2" s="20">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7">
         <v>16</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T2" s="7"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -2303,47 +2399,33 @@
       <c r="E3" s="7">
         <v>12</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="F3" s="7"/>
       <c r="G3" s="7">
         <v>45</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="T3" s="7"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2352,50 +2434,36 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="7">
         <v>51</v>
       </c>
       <c r="G4" s="7">
         <v>30</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="T4" s="7"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -2404,50 +2472,36 @@
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="7">
         <v>9</v>
       </c>
       <c r="J5" s="7">
         <v>11</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="T5" s="7"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -2456,50 +2510,36 @@
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="7">
         <v>50</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
       <c r="J6" s="7">
         <v>17</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="T6" s="7"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2511,21 +2551,11 @@
       <c r="E7" s="7">
         <v>4</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="7">
         <v>7</v>
       </c>
@@ -2550,6 +2580,12 @@
         <v>27</v>
       </c>
       <c r="T7" s="7"/>
+      <c r="U7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2651,6 +2687,7 @@
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="10.42578125" customWidth="1"/>
     <col min="22" max="22" width="9.7109375" customWidth="1"/>
@@ -2671,40 +2708,40 @@
         <v>14</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>50</v>
@@ -2753,9 +2790,9 @@
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N],0)</f>
         <v>14</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="F2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
@@ -2765,50 +2802,86 @@
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>16</v>
       </c>
-      <c r="H2" s="14" t="str">
+      <c r="H2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
-        <v>-</v>
-      </c>
-      <c r="I2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="I2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
-        <v>-</v>
-      </c>
-      <c r="J2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
-        <v>-</v>
-      </c>
-      <c r="K2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="K2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="L2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="M2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="M2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
-        <v>-</v>
-      </c>
-      <c r="N2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="N2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
-        <v>-</v>
-      </c>
-      <c r="O2" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="O2" s="14">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
-        <v>-</v>
-      </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="P2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="T2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="V2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="W2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="X2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="AA2" s="15">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -2820,62 +2893,98 @@
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[N],0)</f>
         <v>12</v>
       </c>
-      <c r="E3" s="14" t="str">
+      <c r="E3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="F3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>45</v>
       </c>
-      <c r="G3" s="14" t="str">
+      <c r="G3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
-        <v>-</v>
-      </c>
-      <c r="H3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
-        <v>-</v>
-      </c>
-      <c r="I3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
-        <v>-</v>
-      </c>
-      <c r="J3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
-        <v>-</v>
-      </c>
-      <c r="K3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="K3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="M3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
-        <v>-</v>
-      </c>
-      <c r="N3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
-        <v>-</v>
-      </c>
-      <c r="O3" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
-        <v>-</v>
-      </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="P3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="X3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="15">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -2883,9 +2992,9 @@
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="14" t="str">
+      <c r="D4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[N],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="E4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
@@ -2895,54 +3004,90 @@
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>30</v>
       </c>
-      <c r="G4" s="14" t="str">
+      <c r="G4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
-        <v>-</v>
-      </c>
-      <c r="H4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
-        <v>-</v>
-      </c>
-      <c r="I4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
-        <v>-</v>
-      </c>
-      <c r="J4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
-        <v>-</v>
-      </c>
-      <c r="K4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="M4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="M4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
-        <v>-</v>
-      </c>
-      <c r="N4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="N4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
-        <v>-</v>
-      </c>
-      <c r="O4" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="O4" s="14">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
-        <v>-</v>
-      </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="15">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -2950,21 +3095,21 @@
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="14" t="str">
+      <c r="D5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[N],0)</f>
-        <v>-</v>
-      </c>
-      <c r="E5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
-        <v>-</v>
-      </c>
-      <c r="F5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
-        <v>-</v>
-      </c>
-      <c r="G5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="H5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
@@ -2974,42 +3119,78 @@
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>11</v>
       </c>
-      <c r="J5" s="14" t="str">
+      <c r="J5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
-        <v>-</v>
-      </c>
-      <c r="K5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="M5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
-        <v>-</v>
-      </c>
-      <c r="N5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
-        <v>-</v>
-      </c>
-      <c r="O5" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="O5" s="14">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
-        <v>-</v>
-      </c>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="15">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -3017,66 +3198,102 @@
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="14" t="str">
+      <c r="D6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[N],0)</f>
-        <v>-</v>
-      </c>
-      <c r="E6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="F6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>50</v>
       </c>
-      <c r="G6" s="14" t="str">
+      <c r="G6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
-        <v>-</v>
-      </c>
-      <c r="H6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="I6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>17</v>
       </c>
-      <c r="J6" s="14" t="str">
+      <c r="J6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
-        <v>-</v>
-      </c>
-      <c r="K6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>-</v>
-      </c>
-      <c r="M6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="M6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
-        <v>-</v>
-      </c>
-      <c r="N6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
-        <v>-</v>
-      </c>
-      <c r="O6" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="O6" s="14">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
-        <v>-</v>
-      </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="14">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="15">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
@@ -3088,25 +3305,25 @@
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[N],0)</f>
         <v>4</v>
       </c>
-      <c r="E7" s="16" t="str">
+      <c r="E7" s="16">
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
-        <v>-</v>
-      </c>
-      <c r="F7" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16">
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
-        <v>-</v>
-      </c>
-      <c r="G7" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16">
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
-        <v>-</v>
-      </c>
-      <c r="H7" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
-        <v>-</v>
-      </c>
-      <c r="I7" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J7" s="16">
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
@@ -3132,98 +3349,170 @@
         <f>_xlfn.XLOOKUP(A7,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0.1</v>
       </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="17"/>
+      <c r="P7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="16">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="17">
+        <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="19"/>
+      <c r="B11" s="19">
+        <f>SUM(tbCore[N ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="19">
+        <f>SUM(tbCore[P ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="19"/>
+      <c r="B13" s="19">
+        <f>SUM(tbCore[K ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="19">
+        <f>SUM(tbCore[Ca ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="19"/>
+      <c r="B15" s="19">
+        <f>SUM(tbCore[Mg ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="19"/>
+      <c r="B16" s="19">
+        <f>SUM(tbCore[S ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="19"/>
+      <c r="B17" s="19">
+        <f>SUM(tbCore[Fe ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="19"/>
+      <c r="B18" s="19">
+        <f>SUM(tbCore[Mn ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="19"/>
+      <c r="B19" s="19">
+        <f>SUM(tbCore[Zn ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="19"/>
+      <c r="B20" s="19">
+        <f>SUM(tbCore[B ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="19">
+        <f>SUM(tbCore[Cu ppm])</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="19">
+        <f>SUM(tbCore[Mo ppm])</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3231,14 +3520,127 @@
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E3A5C77-7B09-4B7F-86F4-56AC8A4C38A6}">
+          <x14:formula1>
+            <xm:f>Fertilizante!$B$2:$B$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20218DE9-EE45-4D44-885E-A900808ADB4D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="21"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="21"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="21"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="21"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="21"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="21"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="21"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="21"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="21"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/Excel/CalcGrower_v0.1.xlsx
+++ b/Excel/CalcGrower_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jefferson\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63897DF2-A9E3-422E-B6B0-4575DEA32A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9834B031-7143-4A5F-B32C-C9096ADBC6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Receitas" sheetId="4" r:id="rId3"/>
     <sheet name="Core" sheetId="8" r:id="rId4"/>
     <sheet name="Resultados" sheetId="6" r:id="rId5"/>
-    <sheet name="Agua" sheetId="3" r:id="rId6"/>
-    <sheet name="Historico" sheetId="7" r:id="rId7"/>
+    <sheet name="Metas" sheetId="9" r:id="rId6"/>
+    <sheet name="Testes" sheetId="10" r:id="rId7"/>
+    <sheet name="Agua" sheetId="3" r:id="rId8"/>
+    <sheet name="Águas" sheetId="11" r:id="rId9"/>
+    <sheet name="Historico" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="119">
   <si>
     <t>Fabricante</t>
   </si>
@@ -66,12 +69,6 @@
     <t>Na</t>
   </si>
   <si>
-    <t>CL</t>
-  </si>
-  <si>
-    <t>Bicarbonato</t>
-  </si>
-  <si>
     <t>Nitrato de cálcio</t>
   </si>
   <si>
@@ -132,33 +129,12 @@
     <t>Produto</t>
   </si>
   <si>
-    <t>Quantidade (g/L)</t>
-  </si>
-  <si>
-    <t>Micromix</t>
-  </si>
-  <si>
-    <t>ID Receita</t>
-  </si>
-  <si>
-    <t>Nome Receita</t>
-  </si>
-  <si>
     <t>Fertilizante</t>
   </si>
   <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>R001</t>
-  </si>
-  <si>
     <t>Vegetativo</t>
   </si>
   <si>
-    <t>Sulfato Mg</t>
-  </si>
-  <si>
     <t>Ferilizante</t>
   </si>
   <si>
@@ -328,6 +304,102 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>Diferença</t>
+  </si>
+  <si>
+    <t>Muda</t>
+  </si>
+  <si>
+    <t>Stretch</t>
+  </si>
+  <si>
+    <t>Floração</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>T003</t>
+  </si>
+  <si>
+    <t>T004</t>
+  </si>
+  <si>
+    <t>g/L</t>
+  </si>
+  <si>
+    <t>Valor Esperado</t>
+  </si>
+  <si>
+    <t>Valor Calculado</t>
+  </si>
+  <si>
+    <t>T005</t>
+  </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>Alvo MVP</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Versão</t>
+  </si>
+  <si>
+    <t>Autor</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Substrato</t>
+  </si>
+  <si>
+    <t>Cultivo</t>
+  </si>
+  <si>
+    <t>Fase</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Água</t>
+  </si>
+  <si>
+    <t>Nome da água</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Temperatura</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>HCO3</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>SO4</t>
   </si>
 </sst>
 </file>
@@ -508,7 +580,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -568,376 +640,137 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+  <dxfs count="146">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -947,41 +780,11 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -997,23 +800,855 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -1023,13 +1658,607 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1669,6 +2898,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1686,13 +2922,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1706,6 +2935,454 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1770,7 +3447,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="145">
   <autoFilter ref="A1:V7" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1796,35 +3473,129 @@
     <filterColumn colId="21" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="0"/>
-    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="142"/>
+    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="141"/>
+    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="140"/>
+    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="139"/>
+    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="138"/>
+    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="137"/>
+    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="136"/>
+    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="135"/>
+    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="134"/>
+    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="133"/>
+    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="132"/>
+    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="131"/>
+    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="130"/>
+    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="129"/>
+    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="128"/>
+    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="127"/>
+    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="126"/>
+    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="125"/>
+    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="124"/>
+    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="123"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="30" tableBorderDxfId="31" totalsRowBorderDxfId="29">
+  <autoFilter ref="D1:E9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="27"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="18" tableBorderDxfId="19" totalsRowBorderDxfId="17">
+  <autoFilter ref="A1:M2" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AA7" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="38" headerRowBorderDxfId="50" tableBorderDxfId="51" totalsRowBorderDxfId="49">
+  <autoFilter ref="A1:J2" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="39"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
+  <autoFilter ref="M1:N2" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="21"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AA7" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117" headerRowBorderDxfId="115" tableBorderDxfId="116" totalsRowBorderDxfId="114">
   <autoFilter ref="A1:AA7" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1855,79 +3626,79 @@
     <filterColumn colId="26" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{071368D0-EBC2-4032-93AC-5DB90A2BD224}" name="ID" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N%" dataDxfId="50">
+    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="112"/>
+    <tableColumn id="3" xr3:uid="{071368D0-EBC2-4032-93AC-5DB90A2BD224}" name="ID" dataDxfId="111"/>
+    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N%" dataDxfId="110">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P%" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P%" dataDxfId="109">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K%" dataDxfId="48">
+    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K%" dataDxfId="108">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[K],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca%" dataDxfId="47">
+    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca%" dataDxfId="107">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg%" dataDxfId="46">
+    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg%" dataDxfId="106">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S%" dataDxfId="45">
+    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S%" dataDxfId="105">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[S],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe%" dataDxfId="44">
+    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe%" dataDxfId="104">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn%" dataDxfId="43">
+    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn%" dataDxfId="103">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn%" dataDxfId="42">
+    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn%" dataDxfId="102">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B%" dataDxfId="41">
+    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B%" dataDxfId="101">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[B],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu%" dataDxfId="40">
+    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu%" dataDxfId="100">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo%" dataDxfId="39">
+    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo%" dataDxfId="99">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="38">
+    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="98">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="37">
+    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="97">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="36">
+    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="96">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="35">
+    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="95">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="34">
+    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="94">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="33">
+    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="93">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="32">
+    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="92">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="31">
+    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="91">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="30">
+    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="90">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="29">
+    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="89">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="28">
+    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="88">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu%]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="27">
+    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="87">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo%]]*10</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1935,15 +3706,109 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="Tabela3" displayName="Tabela3" ref="A10:B22" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="Tabela3" displayName="Tabela3" ref="A10:B22" totalsRowShown="0" headerRowDxfId="122" dataDxfId="121">
   <autoFilter ref="A10:B22" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total" dataDxfId="119"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:E13" totalsRowShown="0" headerRowDxfId="65" dataDxfId="73" headerRowBorderDxfId="71" tableBorderDxfId="72" totalsRowBorderDxfId="70">
+  <autoFilter ref="A1:E13" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="68">
+      <calculatedColumnFormula>Core!B11</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="66">
+      <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="64">
+      <calculatedColumnFormula>IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}" name="Tabela6" displayName="Tabela6" ref="A1:G13" totalsRowShown="0" headerRowDxfId="52" dataDxfId="63" headerRowBorderDxfId="61" tableBorderDxfId="62" totalsRowBorderDxfId="60">
+  <autoFilter ref="A1:G13" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{B9265F24-5305-4F8C-A64E-D1E19AE6DBE5}" name="Nutriente" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{E780DFEA-03ED-48BA-A839-516056C9D710}" name="Alvo MVP" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{F51602EB-33C0-47EE-9CAA-47516B1EA02E}" name="Muda" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{527D4325-9EA7-4C02-B97F-BA2BECB5CA4A}" name="Vegetativo" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{D4E00EE3-4CCE-4EA0-B44D-A949C4D98E69}" name="Stretch" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{1870306A-2CCC-4FAC-B29B-C61803C7A932}" name="Floração" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{45320FC9-9987-45DC-87C6-A47183AC7033}" name="Final" dataDxfId="53"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="76" dataDxfId="86" headerRowBorderDxfId="84" tableBorderDxfId="85" totalsRowBorderDxfId="83">
+  <autoFilter ref="A1:H7" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="75">
+      <calculatedColumnFormula>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="74">
+      <calculatedColumnFormula>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="36" tableBorderDxfId="37" totalsRowBorderDxfId="35">
+  <autoFilter ref="A1:B6" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2253,6 +4118,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2791C869-282C-4C60-88D4-560664883503}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620928F-272B-43F4-861A-5D8E0480B12C}">
   <dimension ref="A1:V7"/>
@@ -2283,25 +4157,25 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
@@ -2310,51 +4184,51 @@
         <v>6</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="U1" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -2377,11 +4251,11 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>5</v>
@@ -2389,10 +4263,10 @@
     </row>
     <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2415,22 +4289,22 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T3" s="7"/>
       <c r="U3" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2453,22 +4327,22 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T4" s="7"/>
       <c r="U4" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -2491,11 +4365,11 @@
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T5" s="7"/>
       <c r="U5" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="V5" s="7" t="s">
         <v>6</v>
@@ -2503,10 +4377,10 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -2529,22 +4403,22 @@
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T6" s="7"/>
       <c r="U6" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2577,14 +4451,14 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T7" s="7"/>
       <c r="U7" s="8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2598,84 +4472,95 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45AD07D-EDA9-4434-8652-C048934E9366}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52">
+        <v>2</v>
+      </c>
+      <c r="J2" s="52"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{81F66671-D486-44F5-BBCF-C4AC82047753}">
+          <x14:formula1>
+            <xm:f>Águas!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2699,90 +4584,90 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="P1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="7"/>
@@ -2885,7 +4770,7 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="7"/>
@@ -2988,7 +4873,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="7"/>
@@ -3091,7 +4976,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="7"/>
@@ -3194,7 +5079,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="7"/>
@@ -3297,7 +5182,7 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
@@ -3400,15 +5285,15 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B11" s="19">
         <f>SUM(tbCore[N ppm])</f>
@@ -3417,7 +5302,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B12" s="19">
         <f>SUM(tbCore[P ppm])</f>
@@ -3426,7 +5311,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B13" s="19">
         <f>SUM(tbCore[K ppm])</f>
@@ -3435,7 +5320,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B14" s="19">
         <f>SUM(tbCore[Ca ppm])</f>
@@ -3444,7 +5329,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B15" s="19">
         <f>SUM(tbCore[Mg ppm])</f>
@@ -3453,7 +5338,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B16" s="19">
         <f>SUM(tbCore[S ppm])</f>
@@ -3462,7 +5347,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B17" s="19">
         <f>SUM(tbCore[Fe ppm])</f>
@@ -3471,7 +5356,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B18" s="19">
         <f>SUM(tbCore[Mn ppm])</f>
@@ -3480,7 +5365,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B19" s="19">
         <f>SUM(tbCore[Zn ppm])</f>
@@ -3489,7 +5374,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B20" s="19">
         <f>SUM(tbCore[B ppm])</f>
@@ -3498,7 +5383,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B21" s="19">
         <f>SUM(tbCore[Cu ppm])</f>
@@ -3507,7 +5392,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B22" s="19">
         <f>SUM(tbCore[Mo ppm])</f>
@@ -3522,7 +5407,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E3A5C77-7B09-4B7F-86F4-56AC8A4C38A6}">
           <x14:formula1>
             <xm:f>Fertilizante!$B$2:$B$7</xm:f>
@@ -3537,172 +5422,816 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20218DE9-EE45-4D44-885E-A900808ADB4D}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="21"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="21"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="21"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="D1" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="41">
+        <f>Core!B11</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41">
+        <f>B2-C2</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="42" t="str">
+        <f t="shared" ref="E2:E13" si="0">IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</f>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="41">
+        <f>Core!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41">
+        <f t="shared" ref="D3:D13" si="1">B3-C3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="41">
+        <f>Core!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="21"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="B5" s="41">
+        <f>Core!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="21"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="21"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="21"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="21"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="21"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="21"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="21"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="21"/>
+      <c r="B6" s="41">
+        <f>Core!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="41">
+        <f>Core!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="41">
+        <f>Core!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="41">
+        <f>Core!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="41">
+        <f>Core!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="41">
+        <f>Core!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="41">
+        <f>Core!B21</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="44">
+        <f>Core!B22</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="44"/>
+      <c r="D13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Ideal</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1500EB1C-D706-4F74-9673-D110E5326842}">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209BE769-EB68-4F67-9D33-FCDE419FF76F}">
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2">
+        <v>175</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="47"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2">
+        <v>55</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="47"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2">
+        <v>225</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="47"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="2">
+        <v>175</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="47"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
+      <c r="B6" s="2">
+        <v>60</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="47"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2">
+        <v>80</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="47"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="47"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="47"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="47"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="47"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="47"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2791C869-282C-4C60-88D4-560664883503}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25C5A9-EE1E-4E82-81B4-649B8D318560}">
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="32" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="32" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="32" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="32" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="32" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Revisar">
+      <formula>NOT(ISERROR(SEARCH("Revisar",H2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Reprovado">
+      <formula>NOT(ISERROR(SEARCH("Reprovado",H2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Aprovado">
+      <formula>NOT(ISERROR(SEARCH("Aprovado",H2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1500EB1C-D706-4F74-9673-D110E5326842}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="D2" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="54"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="D3" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="54"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="54"/>
+      <c r="D4" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="54"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="D5" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="54"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="D6" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="54"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D7" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="54"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="54"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FFBBF4-ED2D-41E2-A29A-72C24AA3FAD6}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="L1" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Excel/CalcGrower_v0.1.xlsx
+++ b/Excel/CalcGrower_v0.1.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A381C40-869E-41B0-98A7-3E7F24F849BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A42FED5-7F48-4EA9-90E0-5FD0923C820B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
     <sheet name="Águas" sheetId="11" r:id="rId2"/>
     <sheet name="Agua" sheetId="3" r:id="rId3"/>
     <sheet name="Fertilizante" sheetId="2" r:id="rId4"/>
-    <sheet name="Metas" sheetId="9" r:id="rId5"/>
+    <sheet name="Perfis Nutricionais" sheetId="14" r:id="rId5"/>
     <sheet name="Formulação" sheetId="7" r:id="rId6"/>
     <sheet name="Core" sheetId="8" r:id="rId7"/>
-    <sheet name="Planilha2" sheetId="13" r:id="rId8"/>
-    <sheet name="Resultados" sheetId="6" r:id="rId9"/>
-    <sheet name="Testes" sheetId="10" r:id="rId10"/>
-    <sheet name="Receitas" sheetId="4" r:id="rId11"/>
+    <sheet name="Resultados" sheetId="6" r:id="rId8"/>
+    <sheet name="Testes" sheetId="10" r:id="rId9"/>
+    <sheet name="Receitas" sheetId="4" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="129">
   <si>
     <t>Fabricante</t>
   </si>
@@ -277,15 +276,9 @@
     <t>Muda</t>
   </si>
   <si>
-    <t>Stretch</t>
-  </si>
-  <si>
     <t>Floração</t>
   </si>
   <si>
-    <t>Final</t>
-  </si>
-  <si>
     <t>T001</t>
   </si>
   <si>
@@ -313,9 +306,6 @@
     <t>T006</t>
   </si>
   <si>
-    <t>Alvo MVP</t>
-  </si>
-  <si>
     <t>Nome</t>
   </si>
   <si>
@@ -370,9 +360,6 @@
     <t>Nome da Receita</t>
   </si>
   <si>
-    <t>Cultivar</t>
-  </si>
-  <si>
     <t>Volume da solução (L)</t>
   </si>
   <si>
@@ -394,30 +381,6 @@
     <t>Diagnóstico Geral</t>
   </si>
   <si>
-    <t>==============================</t>
-  </si>
-  <si>
-    <t>RESUMO</t>
-  </si>
-  <si>
-    <t>Volume:</t>
-  </si>
-  <si>
-    <t>EC Estimado:</t>
-  </si>
-  <si>
-    <t>pH Alvo:</t>
-  </si>
-  <si>
-    <t>Score:</t>
-  </si>
-  <si>
-    <t>Status:</t>
-  </si>
-  <si>
-    <t>CORE ENGINE</t>
-  </si>
-  <si>
     <t>Total ppm</t>
   </si>
   <si>
@@ -425,6 +388,48 @@
   </si>
   <si>
     <t>Massa total (g)</t>
+  </si>
+  <si>
+    <t>Perfil</t>
+  </si>
+  <si>
+    <t>Coco</t>
+  </si>
+  <si>
+    <t>Finalização</t>
+  </si>
+  <si>
+    <t>Perfil Nutricional</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>EC Alvo</t>
+  </si>
+  <si>
+    <t>pH Alvo</t>
+  </si>
+  <si>
+    <t>PF0001</t>
+  </si>
+  <si>
+    <t>PF0002</t>
+  </si>
+  <si>
+    <t>PF0003</t>
+  </si>
+  <si>
+    <t>PF0004</t>
+  </si>
+  <si>
+    <t>Coco Padrão</t>
+  </si>
+  <si>
+    <t>Fotoperiodo</t>
+  </si>
+  <si>
+    <t>Chave</t>
   </si>
 </sst>
 </file>
@@ -487,7 +492,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -606,12 +611,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -726,14 +744,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -754,32 +766,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,9 +789,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -812,7 +806,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -820,9 +826,61 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="163">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+  <dxfs count="176">
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -844,220 +902,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -1073,44 +917,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -1139,6 +945,9 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1176,40 +985,74 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1233,7 +1076,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1257,11 +1099,14 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1277,6 +1122,7 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1299,6 +1145,7 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1321,6 +1168,26 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1343,6 +1210,7 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1365,13 +1233,12 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1387,6 +1254,7 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1409,6 +1277,7 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1431,6 +1300,7 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1453,73 +1323,42 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -1530,452 +1369,40 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
       <border>
         <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+          <color rgb="FF000000"/>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2013,12 +1440,15 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2034,14 +1464,11 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2057,11 +1484,8 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2080,20 +1504,45 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -2103,7 +1552,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2126,7 +1574,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2149,9 +1596,10 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2170,6 +1618,158 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -2193,7 +1793,238 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2283,6 +2114,30 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2747,9 +2602,57 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2993,39 +2896,61 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D08E"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -3034,9 +2959,575 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D08E"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D08E"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -3131,9 +3622,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -3150,9 +3639,7 @@
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -3171,180 +3658,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -3375,7 +3688,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3394,371 +3706,11 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -3774,7 +3726,314 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3926,7 +4185,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="175" headerRowBorderDxfId="174" tableBorderDxfId="173" totalsRowBorderDxfId="172">
   <autoFilter ref="A1:M2" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3943,26 +4202,26 @@
     <filterColumn colId="12" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="171"/>
+    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="170"/>
+    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="169"/>
+    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="168"/>
+    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="167"/>
+    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="166"/>
+    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="165"/>
+    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="164"/>
+    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="163"/>
+    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="162"/>
+    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="161"/>
+    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="160"/>
+    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="159"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:F13" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" totalsRowBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:F13" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
   <autoFilter ref="A1:F13" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3972,21 +4231,21 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="81">
+    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="72">
       <calculatedColumnFormula>Core!B21</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="23">
-      <calculatedColumnFormula>Tabela6[[#This Row],[Alvo MVP]]</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="71">
+      <calculatedColumnFormula>#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="80">
+    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="70">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="79">
+    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="69">
       <calculatedColumnFormula>IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42E27C0C-3B5C-43F0-92FF-2EC97E3D6819}" name="Desvio(%)" dataDxfId="24">
-      <calculatedColumnFormula>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{42E27C0C-3B5C-43F0-92FF-2EC97E3D6819}" name="Desvio(%)" dataDxfId="35">
+      <calculatedColumnFormula>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3994,7 +4253,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63" totalsRowBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <autoFilter ref="A1:H7" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4006,16 +4265,16 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="57">
       <calculatedColumnFormula>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="54">
+    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="56">
       <calculatedColumnFormula>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4024,7 +4283,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="139" headerRowBorderDxfId="138" tableBorderDxfId="137" totalsRowBorderDxfId="136">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <autoFilter ref="A1:J2" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4038,65 +4297,65 @@
     <filterColumn colId="9" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="135"/>
-    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="134"/>
-    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="133"/>
-    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="132"/>
-    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="130"/>
-    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="129"/>
-    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="128"/>
-    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="127"/>
-    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="125" headerRowBorderDxfId="124" tableBorderDxfId="123" totalsRowBorderDxfId="122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
   <autoFilter ref="M1:N2" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="53" headerRowBorderDxfId="52" tableBorderDxfId="51" totalsRowBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="158" headerRowBorderDxfId="157" tableBorderDxfId="156" totalsRowBorderDxfId="155">
   <autoFilter ref="A1:B6" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="154"/>
+    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="153"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="47" headerRowBorderDxfId="46" tableBorderDxfId="45" totalsRowBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="152" headerRowBorderDxfId="151" tableBorderDxfId="150" totalsRowBorderDxfId="149">
   <autoFilter ref="D1:E9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="148"/>
+    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="147"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="162">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="146">
   <autoFilter ref="A1:V7" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4122,36 +4381,36 @@
     <filterColumn colId="21" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="161"/>
-    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="160"/>
-    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="159"/>
-    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="158"/>
-    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="157"/>
-    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="156"/>
-    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="155"/>
-    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="154"/>
-    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="153"/>
-    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="152"/>
-    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="151"/>
-    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="150"/>
-    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="149"/>
-    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="148"/>
-    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="147"/>
-    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="146"/>
-    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="145"/>
-    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="144"/>
-    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="143"/>
-    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="142"/>
-    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="141"/>
-    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="135"/>
+    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="134"/>
+    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="133"/>
+    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="132"/>
+    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="131"/>
+    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="130"/>
+    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="129"/>
+    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="128"/>
+    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="127"/>
+    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="126"/>
+    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="125"/>
+    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}" name="Tabela6" displayName="Tabela6" ref="A1:G13" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
-  <autoFilter ref="A1:G13" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{47AFA806-B900-4990-9D49-0D4746FBA3E2}" name="tbPerfis" displayName="tbPerfis" ref="A1:T5" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" headerRowBorderDxfId="31" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+  <autoFilter ref="A1:T5" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4159,46 +4418,72 @@
     <filterColumn colId="4" hiddenButton="1"/>
     <filterColumn colId="5" hiddenButton="1"/>
     <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+    <filterColumn colId="16" hiddenButton="1"/>
+    <filterColumn colId="17" hiddenButton="1"/>
+    <filterColumn colId="18" hiddenButton="1"/>
+    <filterColumn colId="19" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B9265F24-5305-4F8C-A64E-D1E19AE6DBE5}" name="Nutriente" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{E780DFEA-03ED-48BA-A839-516056C9D710}" name="Alvo MVP" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{F51602EB-33C0-47EE-9CAA-47516B1EA02E}" name="Muda" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{527D4325-9EA7-4C02-B97F-BA2BECB5CA4A}" name="Vegetativo" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{D4E00EE3-4CCE-4EA0-B44D-A949C4D98E69}" name="Stretch" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{1870306A-2CCC-4FAC-B29B-C61803C7A932}" name="Floração" dataDxfId="68"/>
-    <tableColumn id="7" xr3:uid="{45320FC9-9987-45DC-87C6-A47183AC7033}" name="Final" dataDxfId="67"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{99BD0743-D073-411B-8922-2F6240A2828E}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{3E69F40E-30EF-4F89-8554-41124D0E1655}" name="Perfil" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{51BFD522-CD90-4905-A4EF-B43371CE3C70}" name="Substrato" dataDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{D3A33626-1547-466F-8122-B1DD4410B032}" name="Tipo" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{53CC7526-D0B9-443B-8075-2BF3DE35F865}" name="Fase" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{D8298712-C1D8-4E03-A940-5EC770CFB342}" name="EC Alvo" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{04812BD7-7D06-4AEC-A07D-BDFC5645AFA9}" name="pH Alvo" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{862BB450-714B-4731-A40D-55858F0A4302}" name="N" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{DD2EB6AA-16D9-471C-8D4A-7B6F247FEED5}" name="P" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{46410816-6D79-4F2D-9BCE-7851AC64E447}" name="K" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{13AF1400-FEA6-47DD-8C66-B2A6ED2204F0}" name="Ca" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{AABDB186-6991-4CA6-A58F-353DCFE40F19}" name="Mg" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{41D44E74-91B1-4D06-9913-EDE56280C59E}" name="S" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{C9B60923-4291-4761-BDFB-6067669A6E99}" name="Fe" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{ED697F96-0139-4E5F-B4CA-548B2174EDA0}" name="Mn" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{891216E1-A26C-4252-8C78-D70CE50B929A}" name="Zn" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{3750EDF3-9908-473A-876B-70F364037E48}" name="B" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{E8928159-3A8B-4080-96D8-929D2EFCFD04}" name="Cu" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{B158C36F-F317-4E25-8428-CA823201133A}" name="Mo" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{B3ED69D5-ED2B-4F35-B5C4-A8B6110B62F7}" name="Chave" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}" name="Tabela12" displayName="Tabela12" ref="A1:B10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="22" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
-  <autoFilter ref="A1:B10" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}" name="Tabela12" displayName="Tabela12" ref="A1:B11" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:B11" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AACAF1BB-19BB-4915-B77A-B81E0701FC24}" name="Campo" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{76545E86-6D2B-4353-94D9-CF9BDEDF9111}" name="Valor" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{AACAF1BB-19BB-4915-B77A-B81E0701FC24}" name="Campo" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{76545E86-6D2B-4353-94D9-CF9BDEDF9111}" name="Valor" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}" name="Tabela13" displayName="Tabela13" ref="A13:C28" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
-  <autoFilter ref="A13:C28" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}" name="Tabela13" displayName="Tabela13" ref="A14:C29" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="122" tableBorderDxfId="121" totalsRowBorderDxfId="120">
+  <autoFilter ref="A14:C29" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8E817369-B85F-469B-ABBB-1974DD331063}" name="Fertilizante" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{005AB9FD-61D0-418C-AF67-D061C99DF6EB}" name="g/L" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{A30663E6-C900-4C13-AA3B-8BEE5E05CDC8}" name="Quantidade Total (g)" dataDxfId="0">
-      <calculatedColumnFormula>Tabela13[[#This Row],[g/L]]*$B$7</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{8E817369-B85F-469B-ABBB-1974DD331063}" name="Fertilizante" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{005AB9FD-61D0-418C-AF67-D061C99DF6EB}" name="g/L" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{A30663E6-C900-4C13-AA3B-8BEE5E05CDC8}" name="Quantidade Total (g)" dataDxfId="117">
+      <calculatedColumnFormula>Tabela13[[#This Row],[g/L]]*$B$8</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4206,7 +4491,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AC16" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116" totalsRowBorderDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AC16" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
   <autoFilter ref="A1:AC16" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4239,87 +4524,87 @@
     <filterColumn colId="28" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="10">
-      <calculatedColumnFormula>Formulação!A14</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="111">
+      <calculatedColumnFormula>Formulação!A15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="9">
-      <calculatedColumnFormula>Formulação!B14</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="110">
+      <calculatedColumnFormula>Formulação!B15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N" dataDxfId="109">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N]),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P" dataDxfId="114">
+    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P" dataDxfId="108">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K" dataDxfId="113">
+    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K" dataDxfId="107">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[K],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca" dataDxfId="112">
+    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca" dataDxfId="106">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg" dataDxfId="111">
+    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg" dataDxfId="105">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S" dataDxfId="110">
+    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S" dataDxfId="104">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[S],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe" dataDxfId="109">
+    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe" dataDxfId="103">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn" dataDxfId="108">
+    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn" dataDxfId="102">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn" dataDxfId="107">
+    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn" dataDxfId="101">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B" dataDxfId="106">
+    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B" dataDxfId="100">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[B],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu" dataDxfId="105">
+    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu" dataDxfId="99">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo" dataDxfId="104">
+    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo" dataDxfId="98">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F7D91417-A858-4E45-939F-8D2B161C88E2}" name="Custo Total" dataDxfId="13"/>
-    <tableColumn id="28" xr3:uid="{F4771D3F-E3C4-4D9B-9B59-3C575B681CC0}" name="Massa total (g)" dataDxfId="8"/>
-    <tableColumn id="29" xr3:uid="{59357B42-4C96-405A-9DC4-9C5D644AEC14}" name="Status" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{F7D91417-A858-4E45-939F-8D2B161C88E2}" name="Custo Total" dataDxfId="97"/>
+    <tableColumn id="28" xr3:uid="{F4771D3F-E3C4-4D9B-9B59-3C575B681CC0}" name="Massa total (g)" dataDxfId="96"/>
+    <tableColumn id="29" xr3:uid="{59357B42-4C96-405A-9DC4-9C5D644AEC14}" name="Status" dataDxfId="95">
       <calculatedColumnFormula>IF(COUNTA(A2:A16)&gt;0,"✅ Calculando","⚪ Sem dados")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="103">
+    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="94">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="102">
+    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="93">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="101">
+    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="92">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="100">
+    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="91">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="99">
+    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="90">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="98">
+    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="89">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="97">
+    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="88">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="96">
+    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="87">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="95">
+    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="86">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="94">
+    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="85">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="93">
+    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="84">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="92">
+    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="83">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4328,14 +4613,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="tbTotalppm" displayName="tbTotalppm" ref="A20:B32" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="tbTotalppm" displayName="tbTotalppm" ref="A20:B32" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
   <autoFilter ref="A20:B32" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total ppm" dataDxfId="88"/>
+    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total ppm" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4646,197 +4931,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25C5A9-EE1E-4E82-81B4-649B8D318560}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="H2:H7">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Revisar">
-      <formula>NOT(ISERROR(SEARCH("Revisar",H2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="Reprovado">
-      <formula>NOT(ISERROR(SEARCH("Reprovado",H2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Aprovado">
-      <formula>NOT(ISERROR(SEARCH("Aprovado",H2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45AD07D-EDA9-4434-8652-C048934E9366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4856,55 +4950,55 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="E1" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="F1" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="G1" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="H1" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="I1" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="I1" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="44" t="s">
         <v>15</v>
       </c>
       <c r="M1" s="20" t="s">
         <v>28</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="18"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47">
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45">
         <v>2</v>
       </c>
-      <c r="J2" s="47"/>
+      <c r="J2" s="45"/>
       <c r="M2" s="18"/>
       <c r="N2" s="17"/>
     </row>
@@ -4954,56 +5048,56 @@
       <c r="A1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="46" t="s">
+      <c r="B1" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="L1" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="18"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
       <c r="M2" s="17"/>
     </row>
   </sheetData>
@@ -5038,70 +5132,70 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="D2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="49"/>
+      <c r="E2" s="47"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="49"/>
-      <c r="D3" s="48" t="s">
+      <c r="A3" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="47"/>
+      <c r="D3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="49"/>
+      <c r="E3" s="47"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="D4" s="48" t="s">
+      <c r="B4" s="47"/>
+      <c r="D4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="49"/>
+      <c r="E4" s="47"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="D5" s="48" t="s">
+      <c r="B5" s="47"/>
+      <c r="D5" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="49"/>
+      <c r="E5" s="47"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B6" s="17"/>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="47"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D7" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="49"/>
+      <c r="D7" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="47"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="49"/>
+      <c r="D8" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="47"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D9" s="18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E9" s="17"/>
     </row>
@@ -5457,174 +5551,209 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209BE769-EB68-4F67-9D33-FCDE419FF76F}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2332FB-B337-4846-8DE2-3062D44F4039}">
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="1" max="2" width="11.85546875" style="67" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="10.7109375" style="67" customWidth="1"/>
+    <col min="8" max="19" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="70" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="37"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="43"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="43"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="43"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="43"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="43"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="43"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="43"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="43"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="43"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="43"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="43"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="45"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="37"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -5634,10 +5763,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2791C869-282C-4C60-88D4-560664883503}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.7109375" bestFit="1" customWidth="1"/>
@@ -5646,239 +5776,248 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="56" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="F2" s="56"/>
+        <v>104</v>
+      </c>
+      <c r="B2" s="63"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="64"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="57" t="s">
-        <v>117</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="54"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="57"/>
+        <v>119</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="54"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="64"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="57" t="s">
-        <v>118</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="54"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="52"/>
+        <v>93</v>
+      </c>
+      <c r="B6" s="63"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="50"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="64">
-        <v>10</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>119</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B7" s="63"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="50"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="64"/>
-      <c r="F8" s="58"/>
+        <v>105</v>
+      </c>
+      <c r="B8" s="63">
+        <v>1</v>
+      </c>
+      <c r="F8" s="55"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="F9" s="58" t="s">
-        <v>120</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B9" s="63"/>
+      <c r="F9" s="55"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="65"/>
-      <c r="F10" s="58"/>
+      <c r="A10" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="63"/>
+      <c r="F10" s="55"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F11" s="58" t="s">
-        <v>121</v>
-      </c>
+      <c r="A11" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="65"/>
+      <c r="F11" s="55"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" s="58"/>
+      <c r="F12" s="55"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="F13" s="55"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="56"/>
+      <c r="B14" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="55"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="62"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="56" t="s">
-        <v>116</v>
+      <c r="A15" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="62">
+        <v>0.8</v>
+      </c>
+      <c r="C15" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="62"/>
-      <c r="B16" s="72"/>
-      <c r="C16" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
-        <v>0</v>
+      <c r="A16" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="62">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="62"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
-        <v>0</v>
+      <c r="A17" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="62">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="62"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
-        <v>0</v>
+      <c r="A18" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="62">
+        <v>0.35</v>
+      </c>
+      <c r="C18" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
+        <v>0.35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="62"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
-        <v>0</v>
+      <c r="A19" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="62">
+        <v>0.05</v>
+      </c>
+      <c r="C19" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="62"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A20" s="56"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="62"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A21" s="56"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="62"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A22" s="56"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="62"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A23" s="56"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="62"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A24" s="56"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="62"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A25" s="56"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="62"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="73">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A26" s="56"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="63"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="75">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A27" s="56"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="63"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="76">
-        <f>Tabela13[[#This Row],[g/L]]*$B$7</f>
+      <c r="A28" s="56"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="65">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="56"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="65">
+        <f>Tabela13[[#This Row],[g/L]]*$B$8</f>
         <v>0</v>
       </c>
     </row>
@@ -5890,12 +6029,18 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCD27453-F126-4274-B05E-52015DBEDC47}">
           <x14:formula1>
             <xm:f>Fertilizante!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>A14</xm:sqref>
+          <xm:sqref>A15:A29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{12EE4173-3E28-45AE-8D8E-747ECA8FBF2E}">
+          <x14:formula1>
+            <xm:f>'Perfis Nutricionais'!$B$2:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5968,10 +6113,10 @@
         <v>40</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>73</v>
@@ -6014,17 +6159,17 @@
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="66">
-        <f>Formulação!A14</f>
-        <v>0</v>
-      </c>
-      <c r="B2" s="67">
-        <f>Formulação!B14</f>
-        <v>0</v>
+      <c r="A2" s="57" t="str">
+        <f>Formulação!A15</f>
+        <v>Nitrato de cálcio</v>
+      </c>
+      <c r="B2" s="58">
+        <f>Formulação!B15</f>
+        <v>0.8</v>
       </c>
       <c r="C2" s="10">
         <f>IFERROR(_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D2" s="10">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
@@ -6036,7 +6181,7 @@
       </c>
       <c r="F2" s="10">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2" s="10">
         <f>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
@@ -6078,7 +6223,7 @@
       </c>
       <c r="R2" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
-        <v>0</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="S2" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
@@ -6090,7 +6235,7 @@
       </c>
       <c r="U2" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V2" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
@@ -6126,17 +6271,17 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
-        <f>Formulação!A15</f>
-        <v>0</v>
-      </c>
-      <c r="B3" s="67">
-        <f>Formulação!B15</f>
-        <v>0</v>
+      <c r="A3" s="57" t="str">
+        <f>Formulação!A16</f>
+        <v>Nitrato de potássio</v>
+      </c>
+      <c r="B3" s="58">
+        <f>Formulação!B16</f>
+        <v>0.3</v>
       </c>
       <c r="C3" s="10">
         <f>IFERROR(_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D3" s="10">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
@@ -6144,7 +6289,7 @@
       </c>
       <c r="E3" s="10">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F3" s="10">
         <f>_xlfn.XLOOKUP(A3,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
@@ -6190,7 +6335,7 @@
       </c>
       <c r="R3" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="S3" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
@@ -6198,7 +6343,7 @@
       </c>
       <c r="T3" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="U3" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
@@ -6238,13 +6383,13 @@
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
-        <f>Formulação!A16</f>
-        <v>0</v>
-      </c>
-      <c r="B4" s="67">
-        <f>Formulação!B16</f>
-        <v>0</v>
+      <c r="A4" s="57" t="str">
+        <f>Formulação!A17</f>
+        <v>MKP</v>
+      </c>
+      <c r="B4" s="58">
+        <f>Formulação!B17</f>
+        <v>0.2</v>
       </c>
       <c r="C4" s="10">
         <f>IFERROR(_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
@@ -6252,11 +6397,11 @@
       </c>
       <c r="D4" s="10">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E4" s="10">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4" s="10">
         <f>_xlfn.XLOOKUP(A4,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
@@ -6306,11 +6451,11 @@
       </c>
       <c r="S4" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
-        <v>0</v>
+        <v>102.00000000000001</v>
       </c>
       <c r="T4" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="U4" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
@@ -6350,13 +6495,13 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="66">
-        <f>Formulação!A17</f>
-        <v>0</v>
-      </c>
-      <c r="B5" s="67">
-        <f>Formulação!B17</f>
-        <v>0</v>
+      <c r="A5" s="57" t="str">
+        <f>Formulação!A18</f>
+        <v>Sulfato de magnésio</v>
+      </c>
+      <c r="B5" s="58">
+        <f>Formulação!B18</f>
+        <v>0.35</v>
       </c>
       <c r="C5" s="10">
         <f>IFERROR(_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
@@ -6376,11 +6521,11 @@
       </c>
       <c r="G5" s="10">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H5" s="10">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I5" s="10">
         <f>_xlfn.XLOOKUP(A5,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
@@ -6430,11 +6575,11 @@
       </c>
       <c r="V5" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="W5" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="X5" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
@@ -6462,17 +6607,17 @@
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="66">
-        <f>Formulação!A18</f>
-        <v>0</v>
-      </c>
-      <c r="B6" s="67">
-        <f>Formulação!B18</f>
-        <v>0</v>
+      <c r="A6" s="57" t="str">
+        <f>Formulação!A19</f>
+        <v>Micromix Rigrantec</v>
+      </c>
+      <c r="B6" s="58">
+        <f>Formulação!B19</f>
+        <v>0.05</v>
       </c>
       <c r="C6" s="10">
         <f>IFERROR(_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
@@ -6496,27 +6641,27 @@
       </c>
       <c r="I6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N6" s="10">
         <f>_xlfn.XLOOKUP(A6,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
@@ -6526,7 +6671,7 @@
       </c>
       <c r="R6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
@@ -6550,36 +6695,36 @@
       </c>
       <c r="X6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
-        <v>0</v>
+        <v>3.5000000000000004</v>
       </c>
       <c r="Y6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Z6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AB6" s="10">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
-        <v>0</v>
+        <v>0.10000000000000002</v>
       </c>
       <c r="AC6" s="11">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
-        <v>0</v>
+        <v>5.000000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="68">
-        <f>Formulação!A19</f>
-        <v>0</v>
-      </c>
-      <c r="B7" s="69">
-        <f>Formulação!B19</f>
+      <c r="A7" s="59">
+        <f>Formulação!A20</f>
+        <v>0</v>
+      </c>
+      <c r="B7" s="60">
+        <f>Formulação!B20</f>
         <v>0</v>
       </c>
       <c r="C7" s="12">
@@ -6686,59 +6831,59 @@
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="70">
-        <f>Formulação!A20</f>
-        <v>0</v>
-      </c>
-      <c r="B8" s="71">
-        <f>Formulação!B20</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="59">
+      <c r="A8" s="59">
+        <f>Formulação!A21</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="61">
+        <f>Formulação!B21</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="59">
+      <c r="J8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="59">
+      <c r="K8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="59">
+      <c r="L8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="59">
+      <c r="M8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="59">
+      <c r="N8" s="12">
         <f>_xlfn.XLOOKUP(A8,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -6748,109 +6893,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R8" s="59">
+      <c r="R8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S8" s="59">
+      <c r="S8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T8" s="59">
+      <c r="T8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U8" s="59">
+      <c r="U8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V8" s="59">
+      <c r="V8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W8" s="59">
+      <c r="W8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X8" s="59">
+      <c r="X8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y8" s="59">
+      <c r="Y8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="59">
+      <c r="Z8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="59">
+      <c r="AA8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="59">
+      <c r="AB8" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="60">
+      <c r="AC8" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="70">
-        <f>Formulação!A21</f>
-        <v>0</v>
-      </c>
-      <c r="B9" s="71">
-        <f>Formulação!B21</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="59">
+      <c r="A9" s="59">
+        <f>Formulação!A22</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="61">
+        <f>Formulação!B22</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="59">
+      <c r="K9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="59">
+      <c r="L9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="59">
+      <c r="M9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="59">
+      <c r="N9" s="12">
         <f>_xlfn.XLOOKUP(A9,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -6860,109 +7005,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R9" s="59">
+      <c r="R9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S9" s="59">
+      <c r="S9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T9" s="59">
+      <c r="T9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U9" s="59">
+      <c r="U9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V9" s="59">
+      <c r="V9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W9" s="59">
+      <c r="W9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X9" s="59">
+      <c r="X9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="59">
+      <c r="Y9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="59">
+      <c r="Z9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="59">
+      <c r="AA9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB9" s="59">
+      <c r="AB9" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC9" s="60">
+      <c r="AC9" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A10" s="70">
-        <f>Formulação!A22</f>
-        <v>0</v>
-      </c>
-      <c r="B10" s="71">
-        <f>Formulação!B22</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="59">
+      <c r="A10" s="59">
+        <f>Formulação!A23</f>
+        <v>0</v>
+      </c>
+      <c r="B10" s="61">
+        <f>Formulação!B23</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="59">
+      <c r="J10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="59">
+      <c r="M10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="59">
+      <c r="N10" s="12">
         <f>_xlfn.XLOOKUP(A10,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -6972,109 +7117,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R10" s="59">
+      <c r="R10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T10" s="59">
+      <c r="T10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U10" s="59">
+      <c r="U10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V10" s="59">
+      <c r="V10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W10" s="59">
+      <c r="W10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X10" s="59">
+      <c r="X10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="59">
+      <c r="Y10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="59">
+      <c r="Z10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="59">
+      <c r="AA10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="59">
+      <c r="AB10" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="60">
+      <c r="AC10" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="70">
-        <f>Formulação!A23</f>
-        <v>0</v>
-      </c>
-      <c r="B11" s="71">
-        <f>Formulação!B23</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="59">
+      <c r="A11" s="59">
+        <f>Formulação!A24</f>
+        <v>0</v>
+      </c>
+      <c r="B11" s="61">
+        <f>Formulação!B24</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="59">
+      <c r="J11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="59">
+      <c r="L11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="59">
+      <c r="M11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="59">
+      <c r="N11" s="12">
         <f>_xlfn.XLOOKUP(A11,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -7084,109 +7229,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R11" s="59">
+      <c r="R11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S11" s="59">
+      <c r="S11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T11" s="59">
+      <c r="T11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U11" s="59">
+      <c r="U11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V11" s="59">
+      <c r="V11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W11" s="59">
+      <c r="W11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X11" s="59">
+      <c r="X11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="59">
+      <c r="Y11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="59">
+      <c r="Z11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="59">
+      <c r="AA11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="59">
+      <c r="AB11" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC11" s="60">
+      <c r="AC11" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A12" s="70">
-        <f>Formulação!A24</f>
-        <v>0</v>
-      </c>
-      <c r="B12" s="71">
-        <f>Formulação!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="59">
+      <c r="A12" s="59">
+        <f>Formulação!A25</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="61">
+        <f>Formulação!B25</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="59">
+      <c r="E12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="59">
+      <c r="G12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="59">
+      <c r="H12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="59">
+      <c r="J12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="59">
+      <c r="K12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="59">
+      <c r="L12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="59">
+      <c r="M12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="59">
+      <c r="N12" s="12">
         <f>_xlfn.XLOOKUP(A12,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -7196,109 +7341,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R12" s="59">
+      <c r="R12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S12" s="59">
+      <c r="S12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T12" s="59">
+      <c r="T12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U12" s="59">
+      <c r="U12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V12" s="59">
+      <c r="V12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W12" s="59">
+      <c r="W12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X12" s="59">
+      <c r="X12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="59">
+      <c r="Y12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="59">
+      <c r="Z12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="59">
+      <c r="AA12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="59">
+      <c r="AB12" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="60">
+      <c r="AC12" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="70">
-        <f>Formulação!A25</f>
-        <v>0</v>
-      </c>
-      <c r="B13" s="71">
-        <f>Formulação!B25</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="59">
+      <c r="A13" s="59">
+        <f>Formulação!A26</f>
+        <v>0</v>
+      </c>
+      <c r="B13" s="61">
+        <f>Formulação!B26</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="59">
+      <c r="H13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="59">
+      <c r="I13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="59">
+      <c r="J13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="59">
+      <c r="K13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="59">
+      <c r="L13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="59">
+      <c r="M13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="59">
+      <c r="N13" s="12">
         <f>_xlfn.XLOOKUP(A13,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -7308,109 +7453,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R13" s="59">
+      <c r="R13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S13" s="59">
+      <c r="S13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T13" s="59">
+      <c r="T13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U13" s="59">
+      <c r="U13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V13" s="59">
+      <c r="V13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W13" s="59">
+      <c r="W13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X13" s="59">
+      <c r="X13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="59">
+      <c r="Y13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="59">
+      <c r="Z13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="59">
+      <c r="AA13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB13" s="59">
+      <c r="AB13" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="60">
+      <c r="AC13" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A14" s="70">
-        <f>Formulação!A26</f>
-        <v>0</v>
-      </c>
-      <c r="B14" s="71">
-        <f>Formulação!B26</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="59">
+      <c r="A14" s="59">
+        <f>Formulação!A27</f>
+        <v>0</v>
+      </c>
+      <c r="B14" s="61">
+        <f>Formulação!B27</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="59">
+      <c r="E14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="59">
+      <c r="G14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="59">
+      <c r="H14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="59">
+      <c r="I14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="59">
+      <c r="J14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="59">
+      <c r="K14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="59">
+      <c r="L14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="59">
+      <c r="M14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="59">
+      <c r="N14" s="12">
         <f>_xlfn.XLOOKUP(A14,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -7420,109 +7565,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R14" s="59">
+      <c r="R14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S14" s="59">
+      <c r="S14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T14" s="59">
+      <c r="T14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U14" s="59">
+      <c r="U14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V14" s="59">
+      <c r="V14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W14" s="59">
+      <c r="W14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X14" s="59">
+      <c r="X14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="59">
+      <c r="Y14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="59">
+      <c r="Z14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="59">
+      <c r="AA14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="59">
+      <c r="AB14" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="60">
+      <c r="AC14" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A15" s="70">
-        <f>Formulação!A27</f>
-        <v>0</v>
-      </c>
-      <c r="B15" s="71">
-        <f>Formulação!B27</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="59">
+      <c r="A15" s="59">
+        <f>Formulação!A28</f>
+        <v>0</v>
+      </c>
+      <c r="B15" s="61">
+        <f>Formulação!B28</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="59">
+      <c r="H15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="59">
+      <c r="J15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="59">
+      <c r="K15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="59">
+      <c r="L15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="59">
+      <c r="M15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="59">
+      <c r="N15" s="12">
         <f>_xlfn.XLOOKUP(A15,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -7532,109 +7677,109 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R15" s="59">
+      <c r="R15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S15" s="59">
+      <c r="S15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T15" s="59">
+      <c r="T15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U15" s="59">
+      <c r="U15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V15" s="59">
+      <c r="V15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W15" s="59">
+      <c r="W15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X15" s="59">
+      <c r="X15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="59">
+      <c r="Y15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="59">
+      <c r="Z15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="59">
+      <c r="AA15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="59">
+      <c r="AB15" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="60">
+      <c r="AC15" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="70">
-        <f>Formulação!A28</f>
-        <v>0</v>
-      </c>
-      <c r="B16" s="71">
-        <f>Formulação!B28</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="59">
+      <c r="A16" s="59">
+        <f>Formulação!A29</f>
+        <v>0</v>
+      </c>
+      <c r="B16" s="61">
+        <f>Formulação!B29</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[N]),0)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[P],0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[K],0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="59">
+      <c r="F16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="59">
+      <c r="G16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="59">
+      <c r="H16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[S],0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="59">
+      <c r="I16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="59">
+      <c r="J16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="59">
+      <c r="K16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="59">
+      <c r="L16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[B],0)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="59">
+      <c r="M16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="59">
+      <c r="N16" s="12">
         <f>_xlfn.XLOOKUP(A16,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</f>
         <v>0</v>
       </c>
@@ -7644,51 +7789,51 @@
         <f t="shared" si="0"/>
         <v>✅ Calculando</v>
       </c>
-      <c r="R16" s="59">
+      <c r="R16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</f>
         <v>0</v>
       </c>
-      <c r="S16" s="59">
+      <c r="S16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</f>
         <v>0</v>
       </c>
-      <c r="T16" s="59">
+      <c r="T16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</f>
         <v>0</v>
       </c>
-      <c r="U16" s="59">
+      <c r="U16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</f>
         <v>0</v>
       </c>
-      <c r="V16" s="59">
+      <c r="V16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</f>
         <v>0</v>
       </c>
-      <c r="W16" s="59">
+      <c r="W16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</f>
         <v>0</v>
       </c>
-      <c r="X16" s="59">
+      <c r="X16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="59">
+      <c r="Y16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="59">
+      <c r="Z16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="59">
+      <c r="AA16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="59">
+      <c r="AB16" s="12">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="60">
+      <c r="AC16" s="13">
         <f>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</f>
         <v>0</v>
       </c>
@@ -7698,7 +7843,7 @@
         <v>66</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7707,7 +7852,7 @@
       </c>
       <c r="B21" s="15">
         <f>SUM(tbCore[N ppm])</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7716,7 +7861,7 @@
       </c>
       <c r="B22" s="15">
         <f>SUM(tbCore[P ppm])</f>
-        <v>0</v>
+        <v>102.00000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7725,7 +7870,7 @@
       </c>
       <c r="B23" s="15">
         <f>SUM(tbCore[K ppm])</f>
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7734,7 +7879,7 @@
       </c>
       <c r="B24" s="15">
         <f>SUM(tbCore[Ca ppm])</f>
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7743,7 +7888,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(tbCore[Mg ppm])</f>
-        <v>0</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7752,7 +7897,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(tbCore[S ppm])</f>
-        <v>0</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7761,7 +7906,7 @@
       </c>
       <c r="B27" s="15">
         <f>SUM(tbCore[Fe ppm])</f>
-        <v>0</v>
+        <v>3.5000000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7770,7 +7915,7 @@
       </c>
       <c r="B28" s="15">
         <f>SUM(tbCore[Mn ppm])</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7779,7 +7924,7 @@
       </c>
       <c r="B29" s="15">
         <f>SUM(tbCore[Zn ppm])</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7788,7 +7933,7 @@
       </c>
       <c r="B30" s="15">
         <f>SUM(tbCore[B ppm])</f>
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7797,7 +7942,7 @@
       </c>
       <c r="B31" s="15">
         <f>SUM(tbCore[Cu ppm])</f>
-        <v>0</v>
+        <v>0.10000000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7806,7 +7951,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(tbCore[Mo ppm])</f>
-        <v>0</v>
+        <v>5.000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -7819,24 +7964,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC59D9CD-B59F-41DC-BE08-EF4AFAA8456E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20218DE9-EE45-4D44-885E-A900808ADB4D}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7866,36 +7993,36 @@
       <c r="E1" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="54"/>
-    </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="F1" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="52"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="37">
         <f>Core!B21</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="37">
+        <v>150</v>
+      </c>
+      <c r="C2" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D2" s="37" t="e">
         <f>B2-C2</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E2" s="38" t="e">
         <f t="shared" ref="E2:E13" si="0">IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</f>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F2" s="33" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G2" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F2" s="33">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="52"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
@@ -7903,25 +8030,25 @@
       </c>
       <c r="B3" s="37">
         <f>Core!B22</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="37">
+        <v>102.00000000000001</v>
+      </c>
+      <c r="C3" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D3" s="37" t="e">
         <f t="shared" ref="D3:D13" si="1">B3-C3</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E3" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F3" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G3" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F3" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="52"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
@@ -7929,25 +8056,25 @@
       </c>
       <c r="B4" s="37">
         <f>Core!B23</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="37">
+        <v>195</v>
+      </c>
+      <c r="C4" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D4" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E4" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F4" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G4" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F4" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
@@ -7955,25 +8082,25 @@
       </c>
       <c r="B5" s="37">
         <f>Core!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="37">
+        <v>128</v>
+      </c>
+      <c r="C5" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E5" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F5" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F5" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="52"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
@@ -7981,25 +8108,25 @@
       </c>
       <c r="B6" s="37">
         <f>Core!B25</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="37">
+        <v>31.5</v>
+      </c>
+      <c r="C6" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D6" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F6" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F6" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
@@ -8007,25 +8134,25 @@
       </c>
       <c r="B7" s="37">
         <f>Core!B26</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="37">
+        <v>38.5</v>
+      </c>
+      <c r="C7" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D7" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F7" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F7" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="52"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
@@ -8033,25 +8160,25 @@
       </c>
       <c r="B8" s="37">
         <f>Core!B27</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="37">
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="C8" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D8" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F8" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G8" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F8" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
@@ -8059,25 +8186,25 @@
       </c>
       <c r="B9" s="37">
         <f>Core!B28</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="37">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D9" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E9" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F9" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G9" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F9" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="52"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
@@ -8085,25 +8212,25 @@
       </c>
       <c r="B10" s="37">
         <f>Core!B29</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="37">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D10" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F10" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F10" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="52"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
@@ -8111,25 +8238,25 @@
       </c>
       <c r="B11" s="37">
         <f>Core!B30</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="37">
+        <v>0.35</v>
+      </c>
+      <c r="C11" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F11" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G11" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F11" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
@@ -8137,25 +8264,25 @@
       </c>
       <c r="B12" s="37">
         <f>Core!B31</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="37">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="37">
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="C12" s="37" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D12" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="38" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="38" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F12" s="37" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F12" s="37">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="52"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
@@ -8163,29 +8290,29 @@
       </c>
       <c r="B13" s="40">
         <f>Core!B32</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="40">
-        <f>Tabela6[[#This Row],[Alvo MVP]]</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="37">
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="C13" s="40" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D13" s="37" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="41" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="E13" s="41" t="e">
         <f t="shared" si="0"/>
-        <v>🟢 Ideal</v>
-      </c>
-      <c r="F13" s="40" t="e">
-        <f>((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="54"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F13" s="40">
+        <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="52"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16" s="50" t="s">
-        <v>115</v>
+      <c r="K16" s="48" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -8195,4 +8322,195 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25C5A9-EE1E-4E82-81B4-649B8D318560}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Revisar">
+      <formula>NOT(ISERROR(SEARCH("Revisar",H2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Reprovado">
+      <formula>NOT(ISERROR(SEARCH("Reprovado",H2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Aprovado">
+      <formula>NOT(ISERROR(SEARCH("Aprovado",H2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Excel/CalcGrower_v0.1.xlsx
+++ b/Excel/CalcGrower_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jefferson\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A42FED5-7F48-4EA9-90E0-5FD0923C820B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8DD890-56DC-435E-BFCC-070387EC5222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,11 @@
     <sheet name="Fertilizante" sheetId="2" r:id="rId4"/>
     <sheet name="Perfis Nutricionais" sheetId="14" r:id="rId5"/>
     <sheet name="Formulação" sheetId="7" r:id="rId6"/>
-    <sheet name="Core" sheetId="8" r:id="rId7"/>
-    <sheet name="Resultados" sheetId="6" r:id="rId8"/>
-    <sheet name="Testes" sheetId="10" r:id="rId9"/>
-    <sheet name="Receitas" sheetId="4" r:id="rId10"/>
+    <sheet name="Listas" sheetId="15" r:id="rId7"/>
+    <sheet name="Core" sheetId="8" r:id="rId8"/>
+    <sheet name="Resultados" sheetId="6" r:id="rId9"/>
+    <sheet name="Testes" sheetId="10" r:id="rId10"/>
+    <sheet name="Receitas" sheetId="4" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="131">
   <si>
     <t>Fabricante</t>
   </si>
@@ -411,18 +434,6 @@
     <t>pH Alvo</t>
   </si>
   <si>
-    <t>PF0001</t>
-  </si>
-  <si>
-    <t>PF0002</t>
-  </si>
-  <si>
-    <t>PF0003</t>
-  </si>
-  <si>
-    <t>PF0004</t>
-  </si>
-  <si>
     <t>Coco Padrão</t>
   </si>
   <si>
@@ -430,6 +441,24 @@
   </si>
   <si>
     <t>Chave</t>
+  </si>
+  <si>
+    <t>Fotoperíodo</t>
+  </si>
+  <si>
+    <t>Automática</t>
+  </si>
+  <si>
+    <t>PF001</t>
+  </si>
+  <si>
+    <t>PF002</t>
+  </si>
+  <si>
+    <t>PF003</t>
+  </si>
+  <si>
+    <t>PF004</t>
   </si>
 </sst>
 </file>
@@ -629,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -821,35 +850,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="176">
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -881,6 +888,1511 @@
       </fill>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -892,6 +2404,208 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D08E"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D08E"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9D08E"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right/>
         <top style="thin">
           <color indexed="64"/>
@@ -924,30 +2638,30 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -985,6 +2699,1188 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1053,276 +3949,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1379,30 +4005,30 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1422,2602 +4048,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4185,7 +4215,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="175" headerRowBorderDxfId="174" tableBorderDxfId="173" totalsRowBorderDxfId="172">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="150" headerRowBorderDxfId="149" tableBorderDxfId="148" totalsRowBorderDxfId="147">
   <autoFilter ref="A1:M2" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4202,26 +4232,26 @@
     <filterColumn colId="12" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="171"/>
-    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="170"/>
-    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="169"/>
-    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="168"/>
-    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="167"/>
-    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="166"/>
-    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="165"/>
-    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="164"/>
-    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="163"/>
-    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="162"/>
-    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="161"/>
-    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="160"/>
-    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="159"/>
+    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="146"/>
+    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="145"/>
+    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="144"/>
+    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="143"/>
+    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="142"/>
+    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="141"/>
+    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="140"/>
+    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="139"/>
+    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="138"/>
+    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="137"/>
+    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="136"/>
+    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="135"/>
+    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="134"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:F13" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:F13" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
   <autoFilter ref="A1:F13" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4231,20 +4261,20 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="72">
+    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="40">
       <calculatedColumnFormula>Core!B21</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="71">
+    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="39">
       <calculatedColumnFormula>#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="38">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="69">
+    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="37">
       <calculatedColumnFormula>IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42E27C0C-3B5C-43F0-92FF-2EC97E3D6819}" name="Desvio(%)" dataDxfId="35">
+    <tableColumn id="6" xr3:uid="{42E27C0C-3B5C-43F0-92FF-2EC97E3D6819}" name="Desvio(%)" dataDxfId="36">
       <calculatedColumnFormula>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4253,7 +4283,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="31">
   <autoFilter ref="A1:H7" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4265,16 +4295,16 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="57">
+    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="24">
       <calculatedColumnFormula>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="56">
+    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="23">
       <calculatedColumnFormula>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4283,7 +4313,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53" totalsRowBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="A1:J2" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4297,65 +4327,65 @@
     <filterColumn colId="9" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="M1:N2" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="158" headerRowBorderDxfId="157" tableBorderDxfId="156" totalsRowBorderDxfId="155">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="133" headerRowBorderDxfId="132" tableBorderDxfId="131" totalsRowBorderDxfId="130">
   <autoFilter ref="A1:B6" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="154"/>
-    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="153"/>
+    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="128"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="152" headerRowBorderDxfId="151" tableBorderDxfId="150" totalsRowBorderDxfId="149">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="127" headerRowBorderDxfId="126" tableBorderDxfId="125" totalsRowBorderDxfId="124">
   <autoFilter ref="D1:E9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="148"/>
-    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="147"/>
+    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="122"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="121">
   <autoFilter ref="A1:V7" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4381,35 +4411,35 @@
     <filterColumn colId="21" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="137"/>
-    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="135"/>
-    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="134"/>
-    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="133"/>
-    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="132"/>
-    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="131"/>
-    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="130"/>
-    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="129"/>
-    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="128"/>
-    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="127"/>
-    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="126"/>
-    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="125"/>
-    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="112"/>
+    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="111"/>
+    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="110"/>
+    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="109"/>
+    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="108"/>
+    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="107"/>
+    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="106"/>
+    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="105"/>
+    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="104"/>
+    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="103"/>
+    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="102"/>
+    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="101"/>
+    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="100"/>
+    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="99"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{47AFA806-B900-4990-9D49-0D4746FBA3E2}" name="tbPerfis" displayName="tbPerfis" ref="A1:T5" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" headerRowBorderDxfId="31" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{47AFA806-B900-4990-9D49-0D4746FBA3E2}" name="tbPerfis" displayName="tbPerfis" ref="A1:T5" totalsRowShown="0" headerRowDxfId="175" dataDxfId="173" headerRowBorderDxfId="174" tableBorderDxfId="172" totalsRowBorderDxfId="171">
   <autoFilter ref="A1:T5" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4433,56 +4463,56 @@
     <filterColumn colId="19" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{99BD0743-D073-411B-8922-2F6240A2828E}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{3E69F40E-30EF-4F89-8554-41124D0E1655}" name="Perfil" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{51BFD522-CD90-4905-A4EF-B43371CE3C70}" name="Substrato" dataDxfId="27"/>
-    <tableColumn id="17" xr3:uid="{D3A33626-1547-466F-8122-B1DD4410B032}" name="Tipo" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{53CC7526-D0B9-443B-8075-2BF3DE35F865}" name="Fase" dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{D8298712-C1D8-4E03-A940-5EC770CFB342}" name="EC Alvo" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{04812BD7-7D06-4AEC-A07D-BDFC5645AFA9}" name="pH Alvo" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{862BB450-714B-4731-A40D-55858F0A4302}" name="N" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{DD2EB6AA-16D9-471C-8D4A-7B6F247FEED5}" name="P" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{46410816-6D79-4F2D-9BCE-7851AC64E447}" name="K" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{13AF1400-FEA6-47DD-8C66-B2A6ED2204F0}" name="Ca" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{AABDB186-6991-4CA6-A58F-353DCFE40F19}" name="Mg" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{41D44E74-91B1-4D06-9913-EDE56280C59E}" name="S" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{C9B60923-4291-4761-BDFB-6067669A6E99}" name="Fe" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{ED697F96-0139-4E5F-B4CA-548B2174EDA0}" name="Mn" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{891216E1-A26C-4252-8C78-D70CE50B929A}" name="Zn" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{3750EDF3-9908-473A-876B-70F364037E48}" name="B" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{E8928159-3A8B-4080-96D8-929D2EFCFD04}" name="Cu" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{B158C36F-F317-4E25-8428-CA823201133A}" name="Mo" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{B3ED69D5-ED2B-4F35-B5C4-A8B6110B62F7}" name="Chave" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{99BD0743-D073-411B-8922-2F6240A2828E}" name="ID" dataDxfId="170"/>
+    <tableColumn id="2" xr3:uid="{3E69F40E-30EF-4F89-8554-41124D0E1655}" name="Perfil" dataDxfId="169"/>
+    <tableColumn id="3" xr3:uid="{51BFD522-CD90-4905-A4EF-B43371CE3C70}" name="Substrato" dataDxfId="168"/>
+    <tableColumn id="17" xr3:uid="{D3A33626-1547-466F-8122-B1DD4410B032}" name="Tipo" dataDxfId="167"/>
+    <tableColumn id="18" xr3:uid="{53CC7526-D0B9-443B-8075-2BF3DE35F865}" name="Fase" dataDxfId="166"/>
+    <tableColumn id="19" xr3:uid="{D8298712-C1D8-4E03-A940-5EC770CFB342}" name="EC Alvo" dataDxfId="165"/>
+    <tableColumn id="20" xr3:uid="{04812BD7-7D06-4AEC-A07D-BDFC5645AFA9}" name="pH Alvo" dataDxfId="164"/>
+    <tableColumn id="4" xr3:uid="{862BB450-714B-4731-A40D-55858F0A4302}" name="N" dataDxfId="163"/>
+    <tableColumn id="5" xr3:uid="{DD2EB6AA-16D9-471C-8D4A-7B6F247FEED5}" name="P" dataDxfId="162"/>
+    <tableColumn id="6" xr3:uid="{46410816-6D79-4F2D-9BCE-7851AC64E447}" name="K" dataDxfId="161"/>
+    <tableColumn id="7" xr3:uid="{13AF1400-FEA6-47DD-8C66-B2A6ED2204F0}" name="Ca" dataDxfId="160"/>
+    <tableColumn id="9" xr3:uid="{AABDB186-6991-4CA6-A58F-353DCFE40F19}" name="Mg" dataDxfId="159"/>
+    <tableColumn id="10" xr3:uid="{41D44E74-91B1-4D06-9913-EDE56280C59E}" name="S" dataDxfId="158"/>
+    <tableColumn id="12" xr3:uid="{C9B60923-4291-4761-BDFB-6067669A6E99}" name="Fe" dataDxfId="157"/>
+    <tableColumn id="11" xr3:uid="{ED697F96-0139-4E5F-B4CA-548B2174EDA0}" name="Mn" dataDxfId="156"/>
+    <tableColumn id="13" xr3:uid="{891216E1-A26C-4252-8C78-D70CE50B929A}" name="Zn" dataDxfId="155"/>
+    <tableColumn id="14" xr3:uid="{3750EDF3-9908-473A-876B-70F364037E48}" name="B" dataDxfId="154"/>
+    <tableColumn id="15" xr3:uid="{E8928159-3A8B-4080-96D8-929D2EFCFD04}" name="Cu" dataDxfId="153"/>
+    <tableColumn id="16" xr3:uid="{B158C36F-F317-4E25-8428-CA823201133A}" name="Mo" dataDxfId="152"/>
+    <tableColumn id="21" xr3:uid="{B3ED69D5-ED2B-4F35-B5C4-A8B6110B62F7}" name="Chave" dataDxfId="151"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}" name="Tabela12" displayName="Tabela12" ref="A1:B11" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}" name="Tabela12" displayName="Tabela12" ref="A1:B11" totalsRowShown="0" headerRowDxfId="98" dataDxfId="96" headerRowBorderDxfId="97" tableBorderDxfId="95" totalsRowBorderDxfId="94">
   <autoFilter ref="A1:B11" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AACAF1BB-19BB-4915-B77A-B81E0701FC24}" name="Campo" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{76545E86-6D2B-4353-94D9-CF9BDEDF9111}" name="Valor" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{AACAF1BB-19BB-4915-B77A-B81E0701FC24}" name="Campo" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{76545E86-6D2B-4353-94D9-CF9BDEDF9111}" name="Valor" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}" name="Tabela13" displayName="Tabela13" ref="A14:C29" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="122" tableBorderDxfId="121" totalsRowBorderDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}" name="Tabela13" displayName="Tabela13" ref="A14:C29" totalsRowShown="0" headerRowDxfId="91" headerRowBorderDxfId="90" tableBorderDxfId="89" totalsRowBorderDxfId="88">
   <autoFilter ref="A14:C29" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8E817369-B85F-469B-ABBB-1974DD331063}" name="Fertilizante" dataDxfId="119"/>
-    <tableColumn id="2" xr3:uid="{005AB9FD-61D0-418C-AF67-D061C99DF6EB}" name="g/L" dataDxfId="118"/>
-    <tableColumn id="3" xr3:uid="{A30663E6-C900-4C13-AA3B-8BEE5E05CDC8}" name="Quantidade Total (g)" dataDxfId="117">
+    <tableColumn id="1" xr3:uid="{8E817369-B85F-469B-ABBB-1974DD331063}" name="Fertilizante" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{005AB9FD-61D0-418C-AF67-D061C99DF6EB}" name="g/L" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{A30663E6-C900-4C13-AA3B-8BEE5E05CDC8}" name="Quantidade Total (g)" dataDxfId="85">
       <calculatedColumnFormula>Tabela13[[#This Row],[g/L]]*$B$8</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4491,7 +4521,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AC16" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AC16" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
   <autoFilter ref="A1:AC16" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4524,87 +4554,87 @@
     <filterColumn colId="28" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="79">
       <calculatedColumnFormula>Formulação!A15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="110">
+    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="78">
       <calculatedColumnFormula>Formulação!B15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N" dataDxfId="109">
+    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N" dataDxfId="77">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N]),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P" dataDxfId="108">
+    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P" dataDxfId="76">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K" dataDxfId="107">
+    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K" dataDxfId="75">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[K],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca" dataDxfId="106">
+    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca" dataDxfId="74">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg" dataDxfId="105">
+    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg" dataDxfId="73">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S" dataDxfId="104">
+    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S" dataDxfId="72">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[S],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe" dataDxfId="103">
+    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe" dataDxfId="71">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn" dataDxfId="102">
+    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn" dataDxfId="70">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn" dataDxfId="101">
+    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn" dataDxfId="69">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B" dataDxfId="100">
+    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B" dataDxfId="68">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[B],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu" dataDxfId="99">
+    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu" dataDxfId="67">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo" dataDxfId="98">
+    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo" dataDxfId="66">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F7D91417-A858-4E45-939F-8D2B161C88E2}" name="Custo Total" dataDxfId="97"/>
-    <tableColumn id="28" xr3:uid="{F4771D3F-E3C4-4D9B-9B59-3C575B681CC0}" name="Massa total (g)" dataDxfId="96"/>
-    <tableColumn id="29" xr3:uid="{59357B42-4C96-405A-9DC4-9C5D644AEC14}" name="Status" dataDxfId="95">
+    <tableColumn id="3" xr3:uid="{F7D91417-A858-4E45-939F-8D2B161C88E2}" name="Custo Total" dataDxfId="65"/>
+    <tableColumn id="28" xr3:uid="{F4771D3F-E3C4-4D9B-9B59-3C575B681CC0}" name="Massa total (g)" dataDxfId="64"/>
+    <tableColumn id="29" xr3:uid="{59357B42-4C96-405A-9DC4-9C5D644AEC14}" name="Status" dataDxfId="63">
       <calculatedColumnFormula>IF(COUNTA(A2:A16)&gt;0,"✅ Calculando","⚪ Sem dados")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="94">
+    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="62">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="93">
+    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="61">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="92">
+    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="60">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="91">
+    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="59">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="90">
+    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="58">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="89">
+    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="57">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="88">
+    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="56">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="87">
+    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="55">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="86">
+    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="54">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="85">
+    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="53">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="84">
+    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="52">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="83">
+    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="51">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4613,14 +4643,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="tbTotalppm" displayName="tbTotalppm" ref="A20:B32" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="tbTotalppm" displayName="tbTotalppm" ref="A20:B32" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A20:B32" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total ppm" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total ppm" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4931,6 +4961,197 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25C5A9-EE1E-4E82-81B4-649B8D318560}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31">
+        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="str">
+        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
+        <v>✅ Aprovado</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Revisar">
+      <formula>NOT(ISERROR(SEARCH("Revisar",H2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Reprovado">
+      <formula>NOT(ISERROR(SEARCH("Reprovado",H2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Aprovado">
+      <formula>NOT(ISERROR(SEARCH("Aprovado",H2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45AD07D-EDA9-4434-8652-C048934E9366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5621,21 +5842,21 @@
         <v>40</v>
       </c>
       <c r="T1" s="70" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="66" t="s">
         <v>122</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>126</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>116</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E2" s="66" t="s">
         <v>76</v>
@@ -5658,16 +5879,16 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>116</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>29</v>
@@ -5690,16 +5911,16 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>116</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4" s="68" t="s">
         <v>77</v>
@@ -5722,16 +5943,16 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="66" t="s">
         <v>116</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E5" s="68" t="s">
         <v>117</v>
@@ -5781,12 +6002,23 @@
       <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="63"/>
+      <c r="D2" s="71" t="str" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(1,
+(tbPerfis[Perfil]=B7)*
+(tbPerfis[Substrato]=B5)*
+(tbPerfis[Tipo]=B4)*
+(tbPerfis[Fase]=B6),
+tbPerfis[ID],
+"")</f>
+        <v/>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
@@ -5801,7 +6033,9 @@
       <c r="A4" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="63"/>
+      <c r="B4" s="63" t="s">
+        <v>125</v>
+      </c>
       <c r="D4" s="49"/>
       <c r="E4" s="51"/>
       <c r="F4" s="54"/>
@@ -5810,7 +6044,9 @@
       <c r="A5" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="63"/>
+      <c r="B5" s="63" t="s">
+        <v>116</v>
+      </c>
       <c r="D5" s="49"/>
       <c r="E5" s="51"/>
       <c r="F5" s="54"/>
@@ -5819,7 +6055,9 @@
       <c r="A6" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="63"/>
+      <c r="B6" s="63" t="s">
+        <v>29</v>
+      </c>
       <c r="D6" s="49"/>
       <c r="E6" s="51"/>
       <c r="F6" s="50"/>
@@ -5828,7 +6066,9 @@
       <c r="A7" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="63"/>
+      <c r="B7" s="63" t="s">
+        <v>122</v>
+      </c>
       <c r="D7" s="49"/>
       <c r="E7" s="51"/>
       <c r="F7" s="50"/>
@@ -6029,16 +6269,34 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCD27453-F126-4274-B05E-52015DBEDC47}">
           <x14:formula1>
             <xm:f>Fertilizante!$B$2:$B$7</xm:f>
           </x14:formula1>
           <xm:sqref>A15:A29</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{12EE4173-3E28-45AE-8D8E-747ECA8FBF2E}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BD07501E-591E-4974-9299-DC7E9DCFE744}">
           <x14:formula1>
-            <xm:f>'Perfis Nutricionais'!$B$2:$B$5</xm:f>
+            <xm:f>Listas!$A$2:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>B7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A8669DE7-0373-435A-8A52-A50BA193B7D0}">
+          <x14:formula1>
+            <xm:f>Listas!$D$2:$D$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{52D6B8AB-EF55-4A3B-BC83-67A59542C21A}">
+          <x14:formula1>
+            <xm:f>Listas!$B$2:$B$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C869CBD6-66AE-4D6B-A3EB-787B6A82B286}">
+          <x14:formula1>
+            <xm:f>Listas!$C$2:$C$3</xm:f>
           </x14:formula1>
           <xm:sqref>B4</xm:sqref>
         </x14:dataValidation>
@@ -6049,6 +6307,76 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499E135-7EAE-4121-A228-9A5E5755782D}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A151840-C63C-42B6-8105-007C88EE42FE}">
   <dimension ref="A1:AC32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7963,7 +8291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20218DE9-EE45-4D44-885E-A900808ADB4D}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8322,195 +8650,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25C5A9-EE1E-4E82-81B4-649B8D318560}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31">
-        <f>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="28" t="str">
-        <f>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</f>
-        <v>✅ Aprovado</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="H2:H7">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Revisar">
-      <formula>NOT(ISERROR(SEARCH("Revisar",H2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Reprovado">
-      <formula>NOT(ISERROR(SEARCH("Reprovado",H2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Aprovado">
-      <formula>NOT(ISERROR(SEARCH("Aprovado",H2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Excel/CalcGrower_v0.1.xlsx
+++ b/Excel/CalcGrower_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jefferson\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8DD890-56DC-435E-BFCC-070387EC5222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044F340E-0199-4B47-B469-9D5264497E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{460B75DA-C666-464C-971D-95AEB43A337B}"/>
   </bookViews>
@@ -43,30 +43,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="132">
   <si>
     <t>Fabricante</t>
   </si>
@@ -437,9 +415,6 @@
     <t>Coco Padrão</t>
   </si>
   <si>
-    <t>Fotoperiodo</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -459,6 +434,12 @@
   </si>
   <si>
     <t>PF004</t>
+  </si>
+  <si>
+    <t>ID do Perfil</t>
+  </si>
+  <si>
+    <t>1.0</t>
   </si>
 </sst>
 </file>
@@ -658,7 +639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -850,13 +831,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="176">
+  <dxfs count="177">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -4215,7 +4212,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="150" headerRowBorderDxfId="149" tableBorderDxfId="148" totalsRowBorderDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}" name="Tabela11" displayName="Tabela11" ref="A1:M2" totalsRowShown="0" headerRowDxfId="151" headerRowBorderDxfId="150" tableBorderDxfId="149" totalsRowBorderDxfId="148">
   <autoFilter ref="A1:M2" xr:uid="{614F5B07-C6BF-4725-9102-3E3EDC5C905A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4232,26 +4229,26 @@
     <filterColumn colId="12" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="146"/>
-    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="145"/>
-    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="144"/>
-    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="143"/>
-    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="142"/>
-    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="141"/>
-    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="140"/>
-    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="139"/>
-    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="138"/>
-    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="137"/>
-    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="136"/>
-    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="135"/>
-    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="134"/>
+    <tableColumn id="1" xr3:uid="{2D8E22B3-75D9-4903-BC8A-1F75725F661E}" name="ID" dataDxfId="147"/>
+    <tableColumn id="2" xr3:uid="{43D7C108-1B17-4ECA-9CD5-5355A072C0A2}" name="Nome" dataDxfId="146"/>
+    <tableColumn id="3" xr3:uid="{96510E99-B052-496F-84F8-7F47C40A1698}" name="Origem" dataDxfId="145"/>
+    <tableColumn id="4" xr3:uid="{AEC1C91D-35E1-4A6F-93DD-7199E173290D}" name="EC" dataDxfId="144"/>
+    <tableColumn id="5" xr3:uid="{67C7D125-4A24-4EA1-90BF-C67D7DDF982F}" name="pH" dataDxfId="143"/>
+    <tableColumn id="6" xr3:uid="{CA4924ED-FBE8-4C0B-BDF3-6799CD7EE405}" name="Ca" dataDxfId="142"/>
+    <tableColumn id="7" xr3:uid="{725F51A1-80EC-415D-9501-E1E7A0F1F10F}" name="Mg" dataDxfId="141"/>
+    <tableColumn id="8" xr3:uid="{E9D6DC58-72AB-4F03-A4A4-2BFFD4DE797B}" name="Na" dataDxfId="140"/>
+    <tableColumn id="9" xr3:uid="{51D474E6-0780-4668-B50E-9D37BD7383E0}" name="K" dataDxfId="139"/>
+    <tableColumn id="10" xr3:uid="{C3C95CE8-CDC0-474F-BC04-DE373C5BEB77}" name="Fe" dataDxfId="138"/>
+    <tableColumn id="11" xr3:uid="{2291C8F0-5A94-4AE8-BE35-EE88B75DBCAE}" name="CI" dataDxfId="137"/>
+    <tableColumn id="12" xr3:uid="{C81BF974-BA79-4349-80DB-3C91A7AF09E2}" name="SO4" dataDxfId="136"/>
+    <tableColumn id="13" xr3:uid="{F2A99A4F-544F-4E25-9FB7-AA5481DD78CA}" name="HCO3" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:F13" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}" name="Tabela5" displayName="Tabela5" ref="A1:F13" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="A1:F13" xr:uid="{0318362D-90E6-481D-99B5-45B4FA225489}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4261,20 +4258,20 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{EDF15396-0EBF-4123-8D09-4A26E81979CE}" name="Nutriente" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{7C547BD9-ABE0-44C8-812A-D2B0FFDB80B9}" name="ppm" dataDxfId="41">
       <calculatedColumnFormula>Core!B21</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="39">
-      <calculatedColumnFormula>#REF!</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{73EF3B55-CC39-46B0-BBE8-3CBAB4CD724B}" name="Meta" dataDxfId="40">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[N],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="38">
+    <tableColumn id="4" xr3:uid="{EE701742-4F52-4900-9B51-0D69C8F7231B}" name="Diferença" dataDxfId="39">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="37">
+    <tableColumn id="5" xr3:uid="{D8025130-EDA3-47EC-A4B5-F391E4269202}" name="Status" dataDxfId="38">
       <calculatedColumnFormula>IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42E27C0C-3B5C-43F0-92FF-2EC97E3D6819}" name="Desvio(%)" dataDxfId="36">
+    <tableColumn id="6" xr3:uid="{42E27C0C-3B5C-43F0-92FF-2EC97E3D6819}" name="Desvio(%)" dataDxfId="37">
       <calculatedColumnFormula>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4283,7 +4280,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}" name="Tabela4" displayName="Tabela4" ref="A1:H7" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33" totalsRowBorderDxfId="32">
   <autoFilter ref="A1:H7" xr:uid="{5E095CB0-5962-4DCA-82EC-CA07D2D53B95}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4295,16 +4292,16 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{C957C0C9-FA60-4F48-88B0-DC64167313E4}" name="ID" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{1C2102C2-3A41-414B-B0AB-0F012E5F1886}" name="Fertilizante" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{870A6605-2773-45F4-9F8D-CF79C8F90553}" name="g/L" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{68FD7135-EE92-44F1-8F44-2FEE340520E9}" name="Nutriente" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{7C6282C3-C5E9-4F37-BBD5-4CD612942081}" name="Valor Esperado" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{928162D7-31E2-4CE7-B35E-66FFF3E8CD6E}" name="Valor Calculado" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{6DCF56AD-C586-4E6E-8367-F087458B883D}" name="Diferença" dataDxfId="25">
       <calculatedColumnFormula>Tabela4[[#This Row],[Valor Calculado]]-Tabela4[[#This Row],[Valor Esperado]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="23">
+    <tableColumn id="8" xr3:uid="{224572E6-64BC-4633-88CD-A051ED1AC0E0}" name="Status" dataDxfId="24">
       <calculatedColumnFormula>IF(Tabela4[[#This Row],[Diferença]]=0,"✅ Aprovado","❌ Revisar")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4313,7 +4310,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}" name="Tabela7" displayName="Tabela7" ref="A1:J2" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:J2" xr:uid="{6809117B-A72C-47B9-915E-6794D9026216}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4327,65 +4324,65 @@
     <filterColumn colId="9" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{F408CCAE-66DA-4CC1-9140-5BC25CDE01EF}" name="Nome" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{7ECC666C-8736-460A-91E5-F4B38B0ED299}" name="Versão" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{0E37C7D3-AC7C-42F6-84BB-54B66C31DCB5}" name="Autor" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41E99A22-3216-4E99-9C7F-039AC61C1E88}" name="Data" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{3062AEFA-6390-4F9A-85B3-50F1C5C3AF65}" name="Substrato" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{BA3B0C76-A141-4C66-AE29-AC1A8EC28933}" name="Cultivo" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{1C7CC09F-9AE6-408E-91E2-EE578A527C24}" name="Fase" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{985FAABE-70B4-4840-B866-4FB702E672A2}" name="Volume" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{1E8B0D87-ADF9-48B4-A07E-94EBA76349A6}" name="Água" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{677AECB6-F6DE-4F34-A231-67AF99F9D651}" name="Observações" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}" name="Tabela10" displayName="Tabela10" ref="M1:N2" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="M1:N2" xr:uid="{7395E527-A247-4706-A610-7A7386A90AF3}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{EAF276C8-5005-4A6A-ADEC-AACB1266543F}" name="Fertilizante" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{B6F6623B-7A20-4F51-A68C-F227A480C736}" name="g/L" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="133" headerRowBorderDxfId="132" tableBorderDxfId="131" totalsRowBorderDxfId="130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}" name="Tabela8" displayName="Tabela8" ref="A1:B6" totalsRowShown="0" headerRowDxfId="134" headerRowBorderDxfId="133" tableBorderDxfId="132" totalsRowBorderDxfId="131">
   <autoFilter ref="A1:B6" xr:uid="{5A4FCE15-A217-4C91-825C-7CAC0F1BAE4A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="129"/>
-    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="128"/>
+    <tableColumn id="1" xr3:uid="{C6C5F53F-1B7A-46C0-82B4-2ECBBDC12974}" name="Parametro" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{28FD77F5-F0CA-44DF-9C0D-29B98E733881}" name="Valor" dataDxfId="129"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="127" headerRowBorderDxfId="126" tableBorderDxfId="125" totalsRowBorderDxfId="124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}" name="Tabela9" displayName="Tabela9" ref="D1:E9" totalsRowShown="0" headerRowDxfId="128" headerRowBorderDxfId="127" tableBorderDxfId="126" totalsRowBorderDxfId="125">
   <autoFilter ref="D1:E9" xr:uid="{DCE02213-952B-4009-9BF5-D1A23E376292}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="123"/>
-    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="122"/>
+    <tableColumn id="1" xr3:uid="{D792D8BA-29C1-4709-A2D4-9FE188F56B8D}" name="Nutriente" dataDxfId="124"/>
+    <tableColumn id="2" xr3:uid="{CAF141BB-6724-4331-80BC-54820D74EBD9}" name="ppm" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}" name="tbFertilizantes" displayName="tbFertilizantes" ref="A1:V7" totalsRowShown="0" headerRowDxfId="122">
   <autoFilter ref="A1:V7" xr:uid="{E7C143D1-2763-45E0-A650-B62B9F30D4B7}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4411,36 +4408,36 @@
     <filterColumn colId="21" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="120"/>
-    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="119"/>
-    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="118"/>
-    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="117"/>
-    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="115"/>
-    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="114"/>
-    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="113"/>
-    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="112"/>
-    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="111"/>
-    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="110"/>
-    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="109"/>
-    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="108"/>
-    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="107"/>
-    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="106"/>
-    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="105"/>
-    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="104"/>
-    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="103"/>
-    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="102"/>
-    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="101"/>
-    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="100"/>
-    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="99"/>
+    <tableColumn id="1" xr3:uid="{A2D5B959-4CFE-41FF-BC56-0ED245C25662}" name="ID" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{54153458-FF24-4BE8-B3E4-9333239EE6AA}" name="Produto" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{FAD8C287-0303-4CF4-ACB2-1DA5C6009CA4}" name="Fabricante" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{BC5F9AED-CB7E-4034-B0C1-52F67DFF7AC0}" name="Formula" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{AD0F1A8E-626E-4680-9E06-6F4AE92225D5}" name="N" dataDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{C9064F87-9D4A-4F81-BA6E-3F989239C85C}" name="P" dataDxfId="116"/>
+    <tableColumn id="7" xr3:uid="{B1E6223E-C0AE-462D-B234-3496FA6557FE}" name="K" dataDxfId="115"/>
+    <tableColumn id="8" xr3:uid="{87CA8122-2D4E-40D5-8337-3B1170425E83}" name="Ca" dataDxfId="114"/>
+    <tableColumn id="9" xr3:uid="{20D89E3E-02E5-45FB-951D-019143B8D0FD}" name="Mg" dataDxfId="113"/>
+    <tableColumn id="10" xr3:uid="{4331F3AA-3217-4802-8396-EB8F73E23B79}" name="S" dataDxfId="112"/>
+    <tableColumn id="11" xr3:uid="{8774BCE4-E672-4957-BEA8-4C83A072A375}" name="Fe" dataDxfId="111"/>
+    <tableColumn id="12" xr3:uid="{C439FC58-742E-466F-B739-BB7047BA2264}" name="Mn" dataDxfId="110"/>
+    <tableColumn id="13" xr3:uid="{CCF46CA3-6CA5-4697-9E1F-93ED13D77CD3}" name="Zn" dataDxfId="109"/>
+    <tableColumn id="14" xr3:uid="{7A1A50A1-E85A-4BAD-95F2-8203DA737C11}" name="B" dataDxfId="108"/>
+    <tableColumn id="15" xr3:uid="{713E21AF-495B-40E7-BBAB-95882468D61B}" name="Cu" dataDxfId="107"/>
+    <tableColumn id="16" xr3:uid="{95AB7424-53CC-469E-A672-316BEA2C5DD3}" name="Mo" dataDxfId="106"/>
+    <tableColumn id="17" xr3:uid="{F657BD02-0735-413F-999A-3AD63FD4BD12}" name="Solubilidade (g/L)" dataDxfId="105"/>
+    <tableColumn id="18" xr3:uid="{7D18331B-D187-40EA-A416-22BC6D802169}" name="Preço (R$/Kg)" dataDxfId="104"/>
+    <tableColumn id="19" xr3:uid="{517FA329-02F0-4B9D-8205-F5178B426D26}" name="Grupo de concentrado" dataDxfId="103"/>
+    <tableColumn id="20" xr3:uid="{09C2E469-2898-4054-BF94-7E1D2B019E71}" name="Observações" dataDxfId="102"/>
+    <tableColumn id="21" xr3:uid="{FF527B04-6A97-4781-B26B-5BE6D5F7E717}" name="Categoria" dataDxfId="101"/>
+    <tableColumn id="22" xr3:uid="{B9B62B91-2A31-4445-ADEA-C95319A4FBEE}" name="Elemnto Principal" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{47AFA806-B900-4990-9D49-0D4746FBA3E2}" name="tbPerfis" displayName="tbPerfis" ref="A1:T5" totalsRowShown="0" headerRowDxfId="175" dataDxfId="173" headerRowBorderDxfId="174" tableBorderDxfId="172" totalsRowBorderDxfId="171">
-  <autoFilter ref="A1:T5" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{47AFA806-B900-4990-9D49-0D4746FBA3E2}" name="tbPerfis" displayName="tbPerfis" ref="A1:U5" totalsRowShown="0" headerRowDxfId="176" dataDxfId="174" headerRowBorderDxfId="175" tableBorderDxfId="173" totalsRowBorderDxfId="172">
+  <autoFilter ref="A1:U5" xr:uid="{D5BCF4B7-2194-4DB2-B053-8F5A9F56AA4D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4461,58 +4458,62 @@
     <filterColumn colId="17" hiddenButton="1"/>
     <filterColumn colId="18" hiddenButton="1"/>
     <filterColumn colId="19" hiddenButton="1"/>
+    <filterColumn colId="20" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{99BD0743-D073-411B-8922-2F6240A2828E}" name="ID" dataDxfId="170"/>
-    <tableColumn id="2" xr3:uid="{3E69F40E-30EF-4F89-8554-41124D0E1655}" name="Perfil" dataDxfId="169"/>
-    <tableColumn id="3" xr3:uid="{51BFD522-CD90-4905-A4EF-B43371CE3C70}" name="Substrato" dataDxfId="168"/>
-    <tableColumn id="17" xr3:uid="{D3A33626-1547-466F-8122-B1DD4410B032}" name="Tipo" dataDxfId="167"/>
-    <tableColumn id="18" xr3:uid="{53CC7526-D0B9-443B-8075-2BF3DE35F865}" name="Fase" dataDxfId="166"/>
-    <tableColumn id="19" xr3:uid="{D8298712-C1D8-4E03-A940-5EC770CFB342}" name="EC Alvo" dataDxfId="165"/>
-    <tableColumn id="20" xr3:uid="{04812BD7-7D06-4AEC-A07D-BDFC5645AFA9}" name="pH Alvo" dataDxfId="164"/>
-    <tableColumn id="4" xr3:uid="{862BB450-714B-4731-A40D-55858F0A4302}" name="N" dataDxfId="163"/>
-    <tableColumn id="5" xr3:uid="{DD2EB6AA-16D9-471C-8D4A-7B6F247FEED5}" name="P" dataDxfId="162"/>
-    <tableColumn id="6" xr3:uid="{46410816-6D79-4F2D-9BCE-7851AC64E447}" name="K" dataDxfId="161"/>
-    <tableColumn id="7" xr3:uid="{13AF1400-FEA6-47DD-8C66-B2A6ED2204F0}" name="Ca" dataDxfId="160"/>
-    <tableColumn id="9" xr3:uid="{AABDB186-6991-4CA6-A58F-353DCFE40F19}" name="Mg" dataDxfId="159"/>
-    <tableColumn id="10" xr3:uid="{41D44E74-91B1-4D06-9913-EDE56280C59E}" name="S" dataDxfId="158"/>
-    <tableColumn id="12" xr3:uid="{C9B60923-4291-4761-BDFB-6067669A6E99}" name="Fe" dataDxfId="157"/>
-    <tableColumn id="11" xr3:uid="{ED697F96-0139-4E5F-B4CA-548B2174EDA0}" name="Mn" dataDxfId="156"/>
-    <tableColumn id="13" xr3:uid="{891216E1-A26C-4252-8C78-D70CE50B929A}" name="Zn" dataDxfId="155"/>
-    <tableColumn id="14" xr3:uid="{3750EDF3-9908-473A-876B-70F364037E48}" name="B" dataDxfId="154"/>
-    <tableColumn id="15" xr3:uid="{E8928159-3A8B-4080-96D8-929D2EFCFD04}" name="Cu" dataDxfId="153"/>
-    <tableColumn id="16" xr3:uid="{B158C36F-F317-4E25-8428-CA823201133A}" name="Mo" dataDxfId="152"/>
-    <tableColumn id="21" xr3:uid="{B3ED69D5-ED2B-4F35-B5C4-A8B6110B62F7}" name="Chave" dataDxfId="151"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{99BD0743-D073-411B-8922-2F6240A2828E}" name="ID" dataDxfId="171"/>
+    <tableColumn id="8" xr3:uid="{5229E304-0BDB-44BF-BB00-758E4B8FAA89}" name="Versão" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{3E69F40E-30EF-4F89-8554-41124D0E1655}" name="Perfil" dataDxfId="170"/>
+    <tableColumn id="3" xr3:uid="{51BFD522-CD90-4905-A4EF-B43371CE3C70}" name="Substrato" dataDxfId="169"/>
+    <tableColumn id="17" xr3:uid="{D3A33626-1547-466F-8122-B1DD4410B032}" name="Tipo" dataDxfId="168"/>
+    <tableColumn id="18" xr3:uid="{53CC7526-D0B9-443B-8075-2BF3DE35F865}" name="Fase" dataDxfId="167"/>
+    <tableColumn id="19" xr3:uid="{D8298712-C1D8-4E03-A940-5EC770CFB342}" name="EC Alvo" dataDxfId="166"/>
+    <tableColumn id="20" xr3:uid="{04812BD7-7D06-4AEC-A07D-BDFC5645AFA9}" name="pH Alvo" dataDxfId="165"/>
+    <tableColumn id="4" xr3:uid="{862BB450-714B-4731-A40D-55858F0A4302}" name="N" dataDxfId="164"/>
+    <tableColumn id="5" xr3:uid="{DD2EB6AA-16D9-471C-8D4A-7B6F247FEED5}" name="P" dataDxfId="163"/>
+    <tableColumn id="6" xr3:uid="{46410816-6D79-4F2D-9BCE-7851AC64E447}" name="K" dataDxfId="162"/>
+    <tableColumn id="7" xr3:uid="{13AF1400-FEA6-47DD-8C66-B2A6ED2204F0}" name="Ca" dataDxfId="161"/>
+    <tableColumn id="9" xr3:uid="{AABDB186-6991-4CA6-A58F-353DCFE40F19}" name="Mg" dataDxfId="160"/>
+    <tableColumn id="10" xr3:uid="{41D44E74-91B1-4D06-9913-EDE56280C59E}" name="S" dataDxfId="159"/>
+    <tableColumn id="12" xr3:uid="{C9B60923-4291-4761-BDFB-6067669A6E99}" name="Fe" dataDxfId="158"/>
+    <tableColumn id="11" xr3:uid="{ED697F96-0139-4E5F-B4CA-548B2174EDA0}" name="Mn" dataDxfId="157"/>
+    <tableColumn id="13" xr3:uid="{891216E1-A26C-4252-8C78-D70CE50B929A}" name="Zn" dataDxfId="156"/>
+    <tableColumn id="14" xr3:uid="{3750EDF3-9908-473A-876B-70F364037E48}" name="B" dataDxfId="155"/>
+    <tableColumn id="15" xr3:uid="{E8928159-3A8B-4080-96D8-929D2EFCFD04}" name="Cu" dataDxfId="154"/>
+    <tableColumn id="16" xr3:uid="{B158C36F-F317-4E25-8428-CA823201133A}" name="Mo" dataDxfId="153"/>
+    <tableColumn id="21" xr3:uid="{B3ED69D5-ED2B-4F35-B5C4-A8B6110B62F7}" name="Chave" dataDxfId="152">
+      <calculatedColumnFormula>tbPerfis[[#This Row],[Perfil]]&amp;"|"&amp;tbPerfis[[#This Row],[Substrato]]&amp;"|"&amp;tbPerfis[[#This Row],[Tipo]]&amp;"|"&amp;tbPerfis[[#This Row],[Fase]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}" name="Tabela12" displayName="Tabela12" ref="A1:B11" totalsRowShown="0" headerRowDxfId="98" dataDxfId="96" headerRowBorderDxfId="97" tableBorderDxfId="95" totalsRowBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}" name="Tabela12" displayName="Tabela12" ref="A1:B11" totalsRowShown="0" headerRowDxfId="99" dataDxfId="97" headerRowBorderDxfId="98" tableBorderDxfId="96" totalsRowBorderDxfId="95">
   <autoFilter ref="A1:B11" xr:uid="{5EA07ECC-88AA-4B2A-A441-463B836E8D72}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AACAF1BB-19BB-4915-B77A-B81E0701FC24}" name="Campo" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{76545E86-6D2B-4353-94D9-CF9BDEDF9111}" name="Valor" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{AACAF1BB-19BB-4915-B77A-B81E0701FC24}" name="Campo" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{76545E86-6D2B-4353-94D9-CF9BDEDF9111}" name="Valor" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}" name="Tabela13" displayName="Tabela13" ref="A14:C29" totalsRowShown="0" headerRowDxfId="91" headerRowBorderDxfId="90" tableBorderDxfId="89" totalsRowBorderDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}" name="Tabela13" displayName="Tabela13" ref="A14:C29" totalsRowShown="0" headerRowDxfId="92" headerRowBorderDxfId="91" tableBorderDxfId="90" totalsRowBorderDxfId="89">
   <autoFilter ref="A14:C29" xr:uid="{E9969342-0BA2-41AF-A356-D1AD33B7C051}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8E817369-B85F-469B-ABBB-1974DD331063}" name="Fertilizante" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{005AB9FD-61D0-418C-AF67-D061C99DF6EB}" name="g/L" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{A30663E6-C900-4C13-AA3B-8BEE5E05CDC8}" name="Quantidade Total (g)" dataDxfId="85">
+    <tableColumn id="1" xr3:uid="{8E817369-B85F-469B-ABBB-1974DD331063}" name="Fertilizante" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{005AB9FD-61D0-418C-AF67-D061C99DF6EB}" name="g/L" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{A30663E6-C900-4C13-AA3B-8BEE5E05CDC8}" name="Quantidade Total (g)" dataDxfId="86">
       <calculatedColumnFormula>Tabela13[[#This Row],[g/L]]*$B$8</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4521,7 +4522,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AC16" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}" name="tbCore" displayName="tbCore" ref="A1:AC16" totalsRowShown="0" headerRowDxfId="85" dataDxfId="83" headerRowBorderDxfId="84" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <autoFilter ref="A1:AC16" xr:uid="{36D45FC0-2870-4D2D-9F48-65A968840A8A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4554,87 +4555,87 @@
     <filterColumn colId="28" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="79">
+    <tableColumn id="1" xr3:uid="{76144110-7C5B-40DD-9FA1-1804EDDC887A}" name="Ferilizante" dataDxfId="80">
       <calculatedColumnFormula>Formulação!A15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="78">
+    <tableColumn id="2" xr3:uid="{10BA7E9E-ECBA-43AF-8A4F-863888E51EB4}" name=" g/L" dataDxfId="79">
       <calculatedColumnFormula>Formulação!B15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N" dataDxfId="77">
+    <tableColumn id="4" xr3:uid="{071736F8-1715-4240-91AA-D56D2D50F809}" name="N" dataDxfId="78">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[N]),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P" dataDxfId="76">
+    <tableColumn id="5" xr3:uid="{C20B8301-E9FA-4A62-B81D-CB29350E257D}" name="P" dataDxfId="77">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[P],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K" dataDxfId="75">
+    <tableColumn id="6" xr3:uid="{D421A141-BF96-4F56-B9AC-B09E23DE53D5}" name="K" dataDxfId="76">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[K],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca" dataDxfId="74">
+    <tableColumn id="7" xr3:uid="{CDBD4152-9341-40E6-88A4-64B4D0CC74ED}" name="Ca" dataDxfId="75">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Ca],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg" dataDxfId="73">
+    <tableColumn id="8" xr3:uid="{45116017-A258-437E-8AC5-C287F946F1DD}" name="Mg" dataDxfId="74">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mg],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S" dataDxfId="72">
+    <tableColumn id="9" xr3:uid="{5E6F012E-FB69-498B-B71E-2657778768C5}" name="S" dataDxfId="73">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[S],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe" dataDxfId="71">
+    <tableColumn id="10" xr3:uid="{E297B97B-F266-4204-B736-ABABD73533F3}" name="Fe" dataDxfId="72">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Fe],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn" dataDxfId="70">
+    <tableColumn id="11" xr3:uid="{62C497F4-2678-403F-A627-1FE9CF7127CE}" name="Mn" dataDxfId="71">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn" dataDxfId="69">
+    <tableColumn id="12" xr3:uid="{8B9DD9A9-951B-4A1F-AE92-E121ADA4F15D}" name="Zn" dataDxfId="70">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Zn],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B" dataDxfId="68">
+    <tableColumn id="13" xr3:uid="{33AF03BB-0283-4249-858B-C66710803B38}" name="B" dataDxfId="69">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[B],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu" dataDxfId="67">
+    <tableColumn id="14" xr3:uid="{65D972A8-ED42-42E6-BF5D-48A1F25490F9}" name="Cu" dataDxfId="68">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Cu],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo" dataDxfId="66">
+    <tableColumn id="15" xr3:uid="{039C0F97-EF38-4A5C-86D3-A1DCA39C0276}" name="Mo" dataDxfId="67">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,tbFertilizantes[Produto],tbFertilizantes[Mo],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F7D91417-A858-4E45-939F-8D2B161C88E2}" name="Custo Total" dataDxfId="65"/>
-    <tableColumn id="28" xr3:uid="{F4771D3F-E3C4-4D9B-9B59-3C575B681CC0}" name="Massa total (g)" dataDxfId="64"/>
-    <tableColumn id="29" xr3:uid="{59357B42-4C96-405A-9DC4-9C5D644AEC14}" name="Status" dataDxfId="63">
+    <tableColumn id="3" xr3:uid="{F7D91417-A858-4E45-939F-8D2B161C88E2}" name="Custo Total" dataDxfId="66"/>
+    <tableColumn id="28" xr3:uid="{F4771D3F-E3C4-4D9B-9B59-3C575B681CC0}" name="Massa total (g)" dataDxfId="65"/>
+    <tableColumn id="29" xr3:uid="{59357B42-4C96-405A-9DC4-9C5D644AEC14}" name="Status" dataDxfId="64">
       <calculatedColumnFormula>IF(COUNTA(A2:A16)&gt;0,"✅ Calculando","⚪ Sem dados")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="62">
+    <tableColumn id="16" xr3:uid="{577BC5FA-CDBC-48D9-834D-755B12F25F37}" name="N ppm" dataDxfId="63">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[N]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="61">
+    <tableColumn id="17" xr3:uid="{E1244B60-4B82-4279-A888-261864D52E49}" name="P ppm" dataDxfId="62">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[P]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="60">
+    <tableColumn id="18" xr3:uid="{C8DA11C8-87B1-411A-89D8-C3D52F849DB4}" name="K ppm" dataDxfId="61">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[K]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="59">
+    <tableColumn id="19" xr3:uid="{44B282B0-0A73-4207-9B02-E132BC73FB61}" name="Ca ppm" dataDxfId="60">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Ca]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="58">
+    <tableColumn id="20" xr3:uid="{C952A124-2798-4536-A777-9F671ABA262F}" name="Mg ppm" dataDxfId="59">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mg]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="57">
+    <tableColumn id="21" xr3:uid="{C6CAD4D7-1D78-483B-9A41-4E1E64474A78}" name="S ppm" dataDxfId="58">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[S]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="56">
+    <tableColumn id="22" xr3:uid="{6C1FCF1D-7F4A-439A-8EFD-D97B424E9A71}" name="Fe ppm" dataDxfId="57">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Fe]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="55">
+    <tableColumn id="23" xr3:uid="{B3DEFC6B-61B4-4702-9EF7-2775802B94C6}" name="Mn ppm" dataDxfId="56">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mn]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="54">
+    <tableColumn id="24" xr3:uid="{CFEB854B-DD96-4D8D-BC98-87FE925926E1}" name="Zn ppm" dataDxfId="55">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Zn]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="53">
+    <tableColumn id="25" xr3:uid="{61AF59C0-E414-4BBB-913C-376B84FBBBBE}" name="B ppm" dataDxfId="54">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[B]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="52">
+    <tableColumn id="26" xr3:uid="{A344ECD4-6578-48B2-AF50-7AC37612C92E}" name="Cu ppm" dataDxfId="53">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Cu]]*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="51">
+    <tableColumn id="27" xr3:uid="{464B7893-069D-4A89-A3FB-3FC3DF68B950}" name="Mo ppm" dataDxfId="52">
       <calculatedColumnFormula>tbCore[[#This Row],[ g/L]]*tbCore[[#This Row],[Mo]]*10</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4643,14 +4644,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="tbTotalppm" displayName="tbTotalppm" ref="A20:B32" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}" name="tbTotalppm" displayName="tbTotalppm" ref="A20:B32" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A20:B32" xr:uid="{516A8680-E46F-45AF-98A3-60CA5DC72E09}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total ppm" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{EBE2381E-6F61-4F4F-B83A-2D122EAF76D6}" name="Nutriente" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{ED3005D5-F393-4F6C-AAB1-DF3793BF166A}" name="Total ppm" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5134,13 +5135,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H7">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Revisar">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Revisar">
       <formula>NOT(ISERROR(SEARCH("Revisar",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Reprovado">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Reprovado">
       <formula>NOT(ISERROR(SEARCH("Reprovado",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Aprovado">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Aprovado">
       <formula>NOT(ISERROR(SEARCH("Aprovado",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5773,101 +5774,107 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2332FB-B337-4846-8DE2-3062D44F4039}">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.85546875" style="67" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="10.7109375" style="67" customWidth="1"/>
-    <col min="8" max="19" width="5.7109375" customWidth="1"/>
+    <col min="1" max="3" width="11.85546875" style="67" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.7109375" style="67" customWidth="1"/>
+    <col min="9" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="40.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="L1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="Q1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="R1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="S1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="70" t="s">
+      <c r="U1" s="70" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="66" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="66" t="s">
+      <c r="F2" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="66"/>
       <c r="G2" s="66"/>
-      <c r="H2" s="37"/>
+      <c r="H2" s="66"/>
       <c r="I2" s="37"/>
       <c r="J2" s="37"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="33"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="42"/>
       <c r="M2" s="33"/>
       <c r="N2" s="33"/>
       <c r="O2" s="33"/>
@@ -5876,94 +5883,136 @@
       <c r="R2" s="33"/>
       <c r="S2" s="33"/>
       <c r="T2" s="33"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U2" s="33" t="str">
+        <f>tbPerfis[[#This Row],[Perfil]]&amp;"|"&amp;tbPerfis[[#This Row],[Substrato]]&amp;"|"&amp;tbPerfis[[#This Row],[Tipo]]&amp;"|"&amp;tbPerfis[[#This Row],[Fase]]</f>
+        <v>Coco Padrão|Coco|Fotoperíodo|Muda</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="D3" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="8"/>
       <c r="G3" s="8"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="37">
+        <v>160</v>
+      </c>
+      <c r="J3" s="37">
+        <v>45</v>
+      </c>
+      <c r="K3" s="37">
+        <v>200</v>
+      </c>
+      <c r="L3" s="42">
+        <v>160</v>
+      </c>
+      <c r="M3" s="33">
+        <v>55</v>
+      </c>
+      <c r="N3" s="33">
+        <v>70</v>
+      </c>
       <c r="O3" s="40"/>
       <c r="P3" s="40"/>
       <c r="Q3" s="40"/>
       <c r="R3" s="40"/>
       <c r="S3" s="40"/>
-      <c r="T3" s="37"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T3" s="40"/>
+      <c r="U3" s="33" t="str">
+        <f>tbPerfis[[#This Row],[Perfil]]&amp;"|"&amp;tbPerfis[[#This Row],[Substrato]]&amp;"|"&amp;tbPerfis[[#This Row],[Tipo]]&amp;"|"&amp;tbPerfis[[#This Row],[Fase]]</f>
+        <v>Coco Padrão|Coco|Fotoperíodo|Vegetativo</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="D4" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="68"/>
       <c r="G4" s="68"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="40">
+        <v>175</v>
+      </c>
+      <c r="J4" s="40">
+        <v>55</v>
+      </c>
+      <c r="K4" s="40">
+        <v>225</v>
+      </c>
+      <c r="L4" s="43">
+        <v>175</v>
+      </c>
+      <c r="M4" s="40">
+        <v>60</v>
+      </c>
+      <c r="N4" s="40">
+        <v>80</v>
+      </c>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
       <c r="S4" s="40"/>
-      <c r="T4" s="37"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T4" s="40"/>
+      <c r="U4" s="33" t="str">
+        <f>tbPerfis[[#This Row],[Perfil]]&amp;"|"&amp;tbPerfis[[#This Row],[Substrato]]&amp;"|"&amp;tbPerfis[[#This Row],[Tipo]]&amp;"|"&amp;tbPerfis[[#This Row],[Fase]]</f>
+        <v>Coco Padrão|Coco|Fotoperíodo|Floração</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="D5" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="68"/>
       <c r="G5" s="68"/>
-      <c r="H5" s="40"/>
+      <c r="H5" s="68"/>
       <c r="I5" s="40"/>
       <c r="J5" s="40"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="43"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40"/>
       <c r="O5" s="40"/>
@@ -5972,6 +6021,10 @@
       <c r="R5" s="40"/>
       <c r="S5" s="40"/>
       <c r="T5" s="40"/>
+      <c r="U5" s="33" t="str">
+        <f>tbPerfis[[#This Row],[Perfil]]&amp;"|"&amp;tbPerfis[[#This Row],[Substrato]]&amp;"|"&amp;tbPerfis[[#This Row],[Tipo]]&amp;"|"&amp;tbPerfis[[#This Row],[Fase]]</f>
+        <v>Coco Padrão|Coco|Fotoperíodo|Finalização</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -5984,43 +6037,48 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2791C869-282C-4C60-88D4-560664883503}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="71"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" t="str">
+        <f>B7&amp;"|"&amp;B5&amp;"|"&amp;B4&amp;"|"&amp;B6</f>
+        <v>Coco Padrão|Coco|Fotoperíodo|Floração</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="63"/>
-      <c r="D2" s="71" t="str" cm="1">
-        <f t="array" ref="D2">_xlfn.XLOOKUP(1,
-(tbPerfis[Perfil]=B7)*
-(tbPerfis[Substrato]=B5)*
-(tbPerfis[Tipo]=B4)*
-(tbPerfis[Fase]=B6),
-tbPerfis[ID],
-"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" t="str">
+        <f>_xlfn.XLOOKUP(K1,tbPerfis[Chave],tbPerfis[ID],"Perfil não encontrado")</f>
+        <v>PF003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>90</v>
       </c>
@@ -6029,18 +6087,18 @@
       <c r="E3" s="51"/>
       <c r="F3" s="54"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>119</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="49"/>
       <c r="E4" s="51"/>
       <c r="F4" s="54"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>91</v>
       </c>
@@ -6051,18 +6109,18 @@
       <c r="E5" s="51"/>
       <c r="F5" s="54"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>93</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" s="51"/>
       <c r="F6" s="50"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>118</v>
       </c>
@@ -6073,7 +6131,7 @@
       <c r="E7" s="51"/>
       <c r="F7" s="50"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>105</v>
       </c>
@@ -6082,34 +6140,34 @@
       </c>
       <c r="F8" s="55"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>106</v>
       </c>
       <c r="B9" s="63"/>
       <c r="F9" s="55"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>107</v>
       </c>
       <c r="B10" s="63"/>
       <c r="F10" s="55"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
         <v>108</v>
       </c>
       <c r="B11" s="65"/>
       <c r="F11" s="55"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F12" s="55"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F13" s="55"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>28</v>
       </c>
@@ -6121,7 +6179,7 @@
       </c>
       <c r="F14" s="55"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
         <v>8</v>
       </c>
@@ -6133,7 +6191,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
         <v>17</v>
       </c>
@@ -6339,7 +6397,7 @@
         <v>116</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>76</v>
@@ -6349,7 +6407,7 @@
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -8326,7 +8384,7 @@
       </c>
       <c r="G1" s="52"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
         <v>32</v>
       </c>
@@ -8334,25 +8392,25 @@
         <f>Core!B21</f>
         <v>150</v>
       </c>
-      <c r="C2" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D2" s="37" t="e">
+      <c r="C2" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[N],"")</f>
+        <v>175</v>
+      </c>
+      <c r="D2" s="37">
         <f>B2-C2</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E2" s="38" t="e">
+        <v>-25</v>
+      </c>
+      <c r="E2" s="38" t="str">
         <f t="shared" ref="E2:E13" si="0">IF(ABS(D2)&lt;=10,"🟢 Ideal",IF(ABS(D2)&lt;=20,"🟡 Ajustar","🔴 Fora da faixa"))</f>
-        <v>#REF!</v>
+        <v>🔴 Fora da faixa</v>
       </c>
       <c r="F2" s="33">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
-        <v>0</v>
+        <v>-14.285714285714285</v>
       </c>
       <c r="G2" s="52"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
         <v>33</v>
       </c>
@@ -8360,21 +8418,21 @@
         <f>Core!B22</f>
         <v>102.00000000000001</v>
       </c>
-      <c r="C3" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D3" s="37" t="e">
+      <c r="C3" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[P],"")</f>
+        <v>55</v>
+      </c>
+      <c r="D3" s="37">
         <f t="shared" ref="D3:D13" si="1">B3-C3</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="38" t="e">
+        <v>47.000000000000014</v>
+      </c>
+      <c r="E3" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🔴 Fora da faixa</v>
       </c>
       <c r="F3" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
-        <v>0</v>
+        <v>85.454545454545482</v>
       </c>
       <c r="G3" s="52"/>
     </row>
@@ -8386,21 +8444,21 @@
         <f>Core!B23</f>
         <v>195</v>
       </c>
-      <c r="C4" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D4" s="37" t="e">
+      <c r="C4" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[K],"")</f>
+        <v>225</v>
+      </c>
+      <c r="D4" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E4" s="38" t="e">
+        <v>-30</v>
+      </c>
+      <c r="E4" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🔴 Fora da faixa</v>
       </c>
       <c r="F4" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
-        <v>0</v>
+        <v>-13.333333333333334</v>
       </c>
       <c r="G4" s="52"/>
     </row>
@@ -8412,21 +8470,21 @@
         <f>Core!B24</f>
         <v>128</v>
       </c>
-      <c r="C5" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D5" s="37" t="e">
+      <c r="C5" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Ca],"")</f>
+        <v>175</v>
+      </c>
+      <c r="D5" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E5" s="38" t="e">
+        <v>-47</v>
+      </c>
+      <c r="E5" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🔴 Fora da faixa</v>
       </c>
       <c r="F5" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
-        <v>0</v>
+        <v>-26.857142857142858</v>
       </c>
       <c r="G5" s="52"/>
     </row>
@@ -8438,21 +8496,21 @@
         <f>Core!B25</f>
         <v>31.5</v>
       </c>
-      <c r="C6" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D6" s="37" t="e">
+      <c r="C6" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Mg],"")</f>
+        <v>60</v>
+      </c>
+      <c r="D6" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="38" t="e">
+        <v>-28.5</v>
+      </c>
+      <c r="E6" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🔴 Fora da faixa</v>
       </c>
       <c r="F6" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
-        <v>0</v>
+        <v>-47.5</v>
       </c>
       <c r="G6" s="52"/>
     </row>
@@ -8464,21 +8522,21 @@
         <f>Core!B26</f>
         <v>38.5</v>
       </c>
-      <c r="C7" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D7" s="37" t="e">
+      <c r="C7" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[S],"")</f>
+        <v>80</v>
+      </c>
+      <c r="D7" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E7" s="38" t="e">
+        <v>-41.5</v>
+      </c>
+      <c r="E7" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🔴 Fora da faixa</v>
       </c>
       <c r="F7" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
-        <v>0</v>
+        <v>-51.875000000000007</v>
       </c>
       <c r="G7" s="52"/>
     </row>
@@ -8490,17 +8548,17 @@
         <f>Core!B27</f>
         <v>3.5000000000000004</v>
       </c>
-      <c r="C8" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D8" s="37" t="e">
+      <c r="C8" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Fe],"")</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E8" s="38" t="e">
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="E8" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🟢 Ideal</v>
       </c>
       <c r="F8" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
@@ -8516,17 +8574,17 @@
         <f>Core!B28</f>
         <v>0.3</v>
       </c>
-      <c r="C9" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D9" s="37" t="e">
+      <c r="C9" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Mn],"")</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E9" s="38" t="e">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🟢 Ideal</v>
       </c>
       <c r="F9" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
@@ -8542,17 +8600,17 @@
         <f>Core!B29</f>
         <v>0.3</v>
       </c>
-      <c r="C10" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D10" s="37" t="e">
+      <c r="C10" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Zn],"")</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E10" s="38" t="e">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🟢 Ideal</v>
       </c>
       <c r="F10" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
@@ -8568,17 +8626,17 @@
         <f>Core!B30</f>
         <v>0.35</v>
       </c>
-      <c r="C11" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D11" s="37" t="e">
+      <c r="C11" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[B],"")</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E11" s="38" t="e">
+        <v>0.35</v>
+      </c>
+      <c r="E11" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🟢 Ideal</v>
       </c>
       <c r="F11" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
@@ -8594,17 +8652,17 @@
         <f>Core!B31</f>
         <v>0.10000000000000002</v>
       </c>
-      <c r="C12" s="37" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D12" s="37" t="e">
+      <c r="C12" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Cu],"")</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E12" s="38" t="e">
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="E12" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🟢 Ideal</v>
       </c>
       <c r="F12" s="37">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
@@ -8620,17 +8678,17 @@
         <f>Core!B32</f>
         <v>5.000000000000001E-2</v>
       </c>
-      <c r="C13" s="40" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D13" s="37" t="e">
+      <c r="C13" s="37">
+        <f>_xlfn.XLOOKUP(Formulação!$K$2,tbPerfis[ID],tbPerfis[Mo],"")</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="37">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E13" s="41" t="e">
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="E13" s="41" t="str">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>🟢 Ideal</v>
       </c>
       <c r="F13" s="40">
         <f>IFERROR(((Tabela5[[#This Row],[ppm]]-Tabela5[[#This Row],[Meta]])/Tabela5[[#This Row],[Meta]])*100,0)</f>
@@ -8645,6 +8703,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="C2:C13" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
